--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1683-2026</t>
+          <t>A 9956-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1534,14 +1534,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46034</v>
+        <v>44621</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1559,22 +1559,22 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>29.2</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1599,481 +1599,481 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Ögonpyrola
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 1683-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>Skogsalm
 Talltita</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 29532-2022</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>44753</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>4.7</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Backruta
 Hagfingersvamp</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17889-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 7385-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>44971</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>3.5</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bolmört
 Tibast</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17889-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 9956-2022</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 15334-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2083,14 +2083,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45943</v>
+        <v>45019</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2104,17 +2104,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.1</v>
+        <v>27.3</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2148,42 +2148,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15334-2023</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45019</v>
+        <v>45770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,19 +2212,14 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>27.3</v>
+        <v>16.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2258,42 +2253,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58307-2024</t>
+          <t>A 50226-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2303,14 +2298,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45632</v>
+        <v>45943</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2322,14 +2317,19 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2363,35 +2363,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
         <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 58307-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45770</v>
+        <v>45632</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>16.4</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45439</v>
+        <v>45236</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45247</v>
+        <v>44858</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44919</v>
+        <v>45071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,8 +4044,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4088,7 +4093,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4102,10 +4107,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44858</v>
+        <v>45071</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4117,8 +4122,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4161,7 +4171,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4175,10 +4185,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45566</v>
+        <v>45627</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4191,7 +4201,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4234,7 +4244,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4248,10 +4258,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45442</v>
+        <v>45771</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4263,8 +4273,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>16.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4307,7 +4322,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4321,10 +4336,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44974</v>
+        <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4336,8 +4351,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4380,7 +4400,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4390,14 +4410,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45995</v>
+        <v>45548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4409,13 +4429,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4458,7 +4473,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4468,14 +4483,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45071</v>
+        <v>46010</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4493,7 +4508,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4536,7 +4551,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4550,10 +4565,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45071</v>
+        <v>45810</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4567,11 +4582,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>22.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4614,7 +4629,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4624,14 +4639,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45840</v>
+        <v>45789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4643,13 +4658,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4692,7 +4702,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4702,14 +4712,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45840</v>
+        <v>44739</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4721,13 +4731,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4770,7 +4775,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 49311-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4780,14 +4785,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45840</v>
+        <v>44861</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4799,13 +4804,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45846</v>
+        <v>45840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4926,7 +4926,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4936,14 +4936,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45819</v>
+        <v>45840</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4955,8 +4955,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4999,7 +5004,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5009,14 +5014,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46077</v>
+        <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5030,11 +5035,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.2</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5077,7 +5082,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5091,10 +5096,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44998</v>
+        <v>45925</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5106,13 +5111,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5155,7 +5155,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46077</v>
+        <v>44994</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5186,11 +5186,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>19.5</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5233,7 +5233,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5243,14 +5243,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45503</v>
+        <v>45846</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5262,8 +5262,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5306,7 +5311,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5320,10 +5325,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45925</v>
+        <v>44781</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5335,8 +5340,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>22.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5379,7 +5389,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5393,10 +5403,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46078</v>
+        <v>44746</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5410,11 +5420,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>18.6</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5457,7 +5467,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5471,10 +5481,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46093</v>
+        <v>45819</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5487,7 +5497,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5530,7 +5540,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5540,14 +5550,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45722</v>
+        <v>45995</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5561,11 +5571,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>11.5</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5608,7 +5618,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5618,14 +5628,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45705</v>
+        <v>46077</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5643,7 +5653,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>19.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5686,7 +5696,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5700,10 +5710,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44739</v>
+        <v>46078</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5715,8 +5725,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>18.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5759,7 +5774,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5773,10 +5788,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45748</v>
+        <v>46077</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5790,11 +5805,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5837,7 +5852,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 49311-2022</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5851,10 +5866,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44861</v>
+        <v>45446</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5867,7 +5882,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5910,7 +5925,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5924,10 +5939,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45972</v>
+        <v>45566</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5940,7 +5955,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5983,7 +5998,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5997,10 +6012,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46122</v>
+        <v>45635</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6012,13 +6027,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6061,7 +6071,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6075,10 +6085,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46128</v>
+        <v>44919</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6090,13 +6100,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6139,7 +6144,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6153,10 +6158,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46128</v>
+        <v>46093</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6168,13 +6173,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>8.699999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6227,14 +6227,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46128</v>
+        <v>46122</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6312,7 +6312,7 @@
         <v>46122</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6387,10 +6387,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45071</v>
+        <v>46128</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6465,10 +6465,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46134</v>
+        <v>46128</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>13.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6529,7 +6529,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6539,14 +6539,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46134</v>
+        <v>46128</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6607,7 +6607,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46135</v>
+        <v>46134</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>13.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6695,14 +6695,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46010</v>
+        <v>45972</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6714,13 +6714,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6763,7 +6758,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6773,14 +6768,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45236</v>
+        <v>46135</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6792,8 +6787,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6850,10 +6850,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45446</v>
+        <v>46134</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6865,8 +6865,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6909,7 +6914,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6923,10 +6928,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45789</v>
+        <v>45112</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6939,7 +6944,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6982,7 +6987,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6992,14 +6997,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46140</v>
+        <v>45821</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7017,7 +7022,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7060,7 +7065,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7070,14 +7075,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44746</v>
+        <v>46140</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7091,11 +7096,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7138,7 +7143,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7152,10 +7157,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44994</v>
+        <v>46094</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7167,13 +7172,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7216,7 +7216,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44781</v>
+        <v>45222</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7245,13 +7245,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>22.9</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7294,7 +7289,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7308,10 +7303,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44481</v>
+        <v>46150</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7323,8 +7318,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>11.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45821</v>
+        <v>45247</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7396,13 +7396,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7445,7 +7440,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7459,10 +7454,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46094</v>
+        <v>46150</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7474,8 +7469,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7518,7 +7518,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45125</v>
+        <v>46150</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7596,7 +7596,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45627</v>
+        <v>46150</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7625,8 +7625,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7669,7 +7674,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7683,10 +7688,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45771</v>
+        <v>46150</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7704,7 +7709,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>16.8</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7747,7 +7752,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7757,14 +7762,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46150</v>
+        <v>45902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7778,11 +7783,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7825,7 +7830,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7839,10 +7844,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7854,13 +7859,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7903,7 +7903,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7917,10 +7917,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46150</v>
+        <v>46181</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7981,7 +7981,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46150</v>
+        <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8059,7 +8059,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46150</v>
+        <v>46239</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8088,13 +8088,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>11.8</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8132,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8146,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45160</v>
+        <v>46246</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8166,8 +8161,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45635</v>
+        <v>46246</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 33191-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45769</v>
+        <v>46246</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8314,11 +8314,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>10.1</v>
+        <v>4.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8371,14 +8371,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45902</v>
+        <v>45274</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8390,13 +8390,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8439,7 +8434,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8449,14 +8444,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45737</v>
+        <v>46213</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8468,13 +8463,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8517,7 +8507,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8527,14 +8517,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46164</v>
+        <v>46258</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8546,8 +8536,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8590,7 +8585,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8604,10 +8599,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45128</v>
+        <v>45627</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8619,13 +8614,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8668,7 +8658,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8682,10 +8672,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45193</v>
+        <v>46223</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8697,8 +8687,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8741,7 +8736,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8755,10 +8750,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46181</v>
+        <v>46268</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8772,11 +8767,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8819,7 +8814,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8829,14 +8824,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45627</v>
+        <v>46274</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8848,8 +8843,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8892,7 +8892,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8902,14 +8902,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45274</v>
+        <v>46274</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8921,8 +8921,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8965,7 +8970,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8975,14 +8980,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45835</v>
+        <v>46274</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9000,7 +9005,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9043,7 +9048,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9053,14 +9058,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46239</v>
+        <v>46274</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9072,8 +9077,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>5.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9116,7 +9126,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9126,14 +9136,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44953</v>
+        <v>45705</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9145,8 +9155,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9189,7 +9204,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 33191-2026</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9203,10 +9218,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46246</v>
+        <v>45722</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9224,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9267,7 +9282,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9281,10 +9296,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46246</v>
+        <v>44481</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9296,13 +9311,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>7.3</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9345,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9355,14 +9365,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46246</v>
+        <v>45737</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9374,8 +9384,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9418,7 +9433,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9432,10 +9447,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45112</v>
+        <v>45769</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9447,8 +9462,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9491,7 +9511,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9501,14 +9521,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46258</v>
+        <v>45769</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9520,13 +9540,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9569,7 +9584,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9583,10 +9598,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46213</v>
+        <v>45442</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9599,7 +9614,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9642,7 +9657,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9656,10 +9671,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45627</v>
+        <v>44953</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9672,7 +9687,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9715,7 +9730,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9729,10 +9744,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46223</v>
+        <v>45762</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9746,11 +9761,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9808,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9822,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45222</v>
+        <v>44998</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9822,8 +9837,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9886,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9880,10 +9900,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46268</v>
+        <v>45160</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9895,13 +9915,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9944,7 +9959,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9958,10 +9973,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45762</v>
+        <v>45748</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9979,7 +9994,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10022,7 +10037,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10032,14 +10047,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46274</v>
+        <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10057,7 +10072,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10100,7 +10115,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10110,14 +10125,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46274</v>
+        <v>45627</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10129,13 +10144,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10178,7 +10188,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10188,14 +10198,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46274</v>
+        <v>45503</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10207,13 +10217,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10256,7 +10261,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10266,14 +10271,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46274</v>
+        <v>45439</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10285,13 +10290,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10334,7 +10334,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10348,10 +10348,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45769</v>
+        <v>45193</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10363,13 +10363,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>14.6</v>
+        <v>8.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10412,7 +10407,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10429,7 +10424,7 @@
         <v>45769</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10441,8 +10436,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>9</v>
+        <v>14.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10485,7 +10485,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10499,10 +10499,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45632</v>
+        <v>45125</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10514,8 +10514,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10558,7 +10563,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10572,10 +10577,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44764</v>
+        <v>44974</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10588,7 +10593,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10631,7 +10636,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10645,10 +10650,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44998</v>
+        <v>45632</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10660,13 +10665,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>6.9</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10709,7 +10709,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10723,10 +10723,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45785</v>
+        <v>44998</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10740,11 +10740,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>18</v>
+        <v>6.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10787,7 +10787,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10801,10 +10801,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45785</v>
+        <v>44764</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10816,13 +10816,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10865,7 +10860,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10879,10 +10874,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45627</v>
+        <v>45785</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10894,8 +10889,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2.7</v>
+        <v>6.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10938,7 +10938,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10952,10 +10952,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45635</v>
+        <v>45785</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10967,8 +10967,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>2.1</v>
+        <v>18</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11011,7 +11016,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11025,10 +11030,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45548</v>
+        <v>45627</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11041,7 +11046,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11084,7 +11089,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11098,10 +11103,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45810</v>
+        <v>45635</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11113,13 +11118,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>22.6</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11179,7 +11179,7 @@
         <v>45840</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45840</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45840</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45846</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>46010</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46128</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>46135</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>46258</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>46274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 9956-2022</t>
+          <t>A 29532-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44621</v>
+        <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,22 +1553,17 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1583,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1599,481 +1594,486 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Backruta
+Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 17889-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 7385-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44971</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Bolmört
+Tibast</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 1683-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Talltita</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9956-2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Ögonpyrola
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 1683-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46034</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Talltita</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 29532-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44753</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Backruta
-Hagfingersvamp</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17889-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 7385-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44971</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Tibast</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15334-2023</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45019</v>
+        <v>45770</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2102,19 +2102,14 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>27.3</v>
+        <v>16.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2148,42 +2143,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 3553-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2197,10 +2192,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45770</v>
+        <v>46042</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2213,17 +2208,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>16.4</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2237,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2253,42 +2248,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 15334-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2298,14 +2293,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45943</v>
+        <v>45019</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2319,17 +2314,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.1</v>
+        <v>27.3</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2363,42 +2358,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 3553-2026</t>
+          <t>A 58307-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2412,10 +2407,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46042</v>
+        <v>45632</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,16 +2423,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2452,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2468,42 +2463,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58307-2024</t>
+          <t>A 50226-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2513,14 +2508,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45632</v>
+        <v>45943</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2532,14 +2527,19 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 51936-2022</t>
+          <t>A 25053-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44872</v>
+        <v>44729</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 25053-2022</t>
+          <t>A 25057-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 25057-2022</t>
+          <t>A 69104-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44729</v>
+        <v>44530</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3669,8 +3669,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3713,7 +3718,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 69104-2021</t>
+          <t>A 68174-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3727,10 +3732,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44530</v>
+        <v>44526</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3744,11 +3749,11 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3791,7 +3796,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 68174-2021</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3805,10 +3810,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44526</v>
+        <v>45193</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3820,13 +3825,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>8.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3869,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 51936-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3879,14 +3879,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45236</v>
+        <v>44872</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44858</v>
+        <v>45439</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>6.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45071</v>
+        <v>45247</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,13 +4044,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4093,7 +4088,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4107,10 +4102,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45071</v>
+        <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4124,11 +4119,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>18.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4171,7 +4166,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4185,10 +4180,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45627</v>
+        <v>44919</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4201,7 +4196,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4244,7 +4239,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4258,10 +4253,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45771</v>
+        <v>44858</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4273,13 +4268,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>16.8</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4322,7 +4312,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4336,10 +4326,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45128</v>
+        <v>46093</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4351,13 +4341,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4400,7 +4385,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4414,10 +4399,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45548</v>
+        <v>45566</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4430,7 +4415,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4473,7 +4458,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4483,14 +4468,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46010</v>
+        <v>45442</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4502,13 +4487,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4551,7 +4531,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4565,10 +4545,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45810</v>
+        <v>45627</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4580,13 +4560,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>22.6</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4629,7 +4604,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4643,10 +4618,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45789</v>
+        <v>45274</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4659,7 +4634,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4702,7 +4677,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4716,10 +4691,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44739</v>
+        <v>45925</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4732,7 +4707,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4775,7 +4750,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49311-2022</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4789,10 +4764,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44861</v>
+        <v>46122</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4804,8 +4779,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4848,7 +4828,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4858,14 +4838,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45840</v>
+        <v>44974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4877,13 +4857,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>8.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4926,7 +4901,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4936,14 +4911,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45840</v>
+        <v>46128</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4961,7 +4936,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5004,7 +4979,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5014,14 +4989,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45840</v>
+        <v>46128</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5039,7 +5014,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5082,7 +5057,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5092,14 +5067,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45925</v>
+        <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5111,8 +5086,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5155,7 +5135,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5169,10 +5149,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44994</v>
+        <v>46122</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5186,11 +5166,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>6.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5233,7 +5213,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5243,14 +5223,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45846</v>
+        <v>46134</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5268,7 +5248,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>13.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5311,7 +5291,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5321,14 +5301,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44781</v>
+        <v>45071</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5342,11 +5322,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>22.9</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5389,7 +5369,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5403,10 +5383,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44746</v>
+        <v>45071</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5420,11 +5400,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5467,7 +5447,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5481,10 +5461,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45819</v>
+        <v>46134</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5496,8 +5476,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5540,7 +5525,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5554,10 +5539,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45995</v>
+        <v>46135</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5571,11 +5556,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5618,7 +5603,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5632,10 +5617,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46077</v>
+        <v>44953</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5647,13 +5632,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>19.5</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5696,7 +5676,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5710,10 +5690,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46078</v>
+        <v>44998</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5727,11 +5707,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>18.6</v>
+        <v>3.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5774,7 +5754,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5784,14 +5764,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46077</v>
+        <v>46140</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5805,11 +5785,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5852,7 +5832,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5866,10 +5846,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45446</v>
+        <v>45972</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5882,7 +5862,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5925,7 +5905,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5939,10 +5919,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45566</v>
+        <v>45503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5955,7 +5935,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5998,7 +5978,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6012,10 +5992,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45635</v>
+        <v>45821</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6027,8 +6007,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6071,7 +6056,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6085,10 +6070,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44919</v>
+        <v>46094</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6101,7 +6086,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6144,7 +6129,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6158,10 +6143,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46093</v>
+        <v>45722</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6173,8 +6158,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>11.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6217,7 +6207,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6231,10 +6221,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46122</v>
+        <v>45112</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6246,13 +6236,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6295,7 +6280,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6309,10 +6294,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46122</v>
+        <v>46150</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6330,7 +6315,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.9</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6373,7 +6358,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6387,10 +6372,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46128</v>
+        <v>46150</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6408,7 +6393,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6451,7 +6436,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6465,10 +6450,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46128</v>
+        <v>46150</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6486,7 +6471,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6529,7 +6514,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6539,14 +6524,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46128</v>
+        <v>46150</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6564,7 +6549,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6607,7 +6592,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6621,10 +6606,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46134</v>
+        <v>46150</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6642,7 +6627,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6685,7 +6670,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6695,14 +6680,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45972</v>
+        <v>45705</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6714,8 +6699,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>5.4</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6758,7 +6748,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6768,14 +6758,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46135</v>
+        <v>44739</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6787,13 +6777,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6836,7 +6821,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6850,10 +6835,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46134</v>
+        <v>45748</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6871,7 +6856,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6914,7 +6899,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6924,14 +6909,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45112</v>
+        <v>46010</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6943,8 +6928,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6987,7 +6977,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6997,14 +6987,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45821</v>
+        <v>45902</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7018,11 +7008,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7065,7 +7055,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 49311-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7075,14 +7065,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46140</v>
+        <v>44861</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7094,13 +7084,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7143,7 +7128,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7157,10 +7142,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46094</v>
+        <v>45789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7173,7 +7158,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7216,7 +7201,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7230,10 +7215,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45222</v>
+        <v>46164</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7246,7 +7231,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>6.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7289,7 +7274,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7303,10 +7288,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46150</v>
+        <v>45071</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7324,7 +7309,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>11.8</v>
+        <v>2.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7367,7 +7352,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7381,10 +7366,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45247</v>
+        <v>46181</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7396,8 +7381,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7440,7 +7430,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7454,10 +7444,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46150</v>
+        <v>45236</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7469,13 +7459,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7518,7 +7503,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7532,10 +7517,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46150</v>
+        <v>45446</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7547,13 +7532,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7596,7 +7576,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7610,10 +7590,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46150</v>
+        <v>44746</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7627,11 +7607,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.1</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7674,7 +7654,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7688,10 +7668,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46150</v>
+        <v>44994</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7705,11 +7685,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7752,7 +7732,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7762,14 +7742,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45902</v>
+        <v>44781</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7787,7 +7767,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>22.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7830,7 +7810,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7840,14 +7820,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46164</v>
+        <v>45995</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7859,8 +7839,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7903,7 +7888,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7917,10 +7902,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46181</v>
+        <v>46077</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7934,11 +7919,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7981,7 +7966,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7995,10 +7980,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45835</v>
+        <v>46077</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8012,11 +7997,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.5</v>
+        <v>19.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8059,7 +8044,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8073,10 +8058,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46239</v>
+        <v>45835</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8088,8 +8073,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8132,7 +8122,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8146,10 +8136,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46246</v>
+        <v>46239</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8161,13 +8151,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>7.3</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8195,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8209,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46246</v>
+        <v>44481</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8225,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8300,7 +8285,7 @@
         <v>46246</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8361,7 +8346,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8375,10 +8360,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45274</v>
+        <v>46246</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8390,8 +8375,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8434,7 +8424,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8448,10 +8438,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46213</v>
+        <v>46246</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8464,7 +8454,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8507,7 +8497,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8517,14 +8507,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46258</v>
+        <v>45125</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8542,7 +8532,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8585,7 +8575,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8602,7 +8592,7 @@
         <v>45627</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8615,7 +8605,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8658,7 +8648,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8672,10 +8662,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46223</v>
+        <v>45771</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8689,11 +8679,11 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.4</v>
+        <v>16.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8736,7 +8726,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8750,10 +8740,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46268</v>
+        <v>45627</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8765,13 +8755,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8814,7 +8799,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8824,14 +8809,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46274</v>
+        <v>45160</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8843,13 +8828,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8892,7 +8872,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8902,14 +8882,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46274</v>
+        <v>45635</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8921,13 +8901,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8970,7 +8945,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8980,14 +8955,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46274</v>
+        <v>45769</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9001,11 +8976,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6.5</v>
+        <v>10.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9048,7 +9023,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9058,14 +9033,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46274</v>
+        <v>45737</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9079,11 +9054,11 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9126,7 +9101,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9136,14 +9111,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45705</v>
+        <v>46258</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9157,11 +9132,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.2</v>
+        <v>6.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9204,7 +9179,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9218,10 +9193,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45722</v>
+        <v>46213</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9233,13 +9208,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>11.5</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9282,7 +9252,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9296,10 +9266,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44481</v>
+        <v>45222</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9312,7 +9282,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9355,7 +9325,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9365,14 +9335,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45737</v>
+        <v>45128</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9386,11 +9356,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9433,7 +9403,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9447,10 +9417,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45769</v>
+        <v>46223</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9464,11 +9434,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>10.1</v>
+        <v>4.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9511,7 +9481,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9525,10 +9495,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45769</v>
+        <v>45762</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9540,8 +9510,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9584,7 +9559,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9598,10 +9573,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45442</v>
+        <v>46268</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9613,8 +9588,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9657,7 +9637,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9667,14 +9647,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44953</v>
+        <v>46274</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9686,8 +9666,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9730,7 +9715,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9740,14 +9725,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45762</v>
+        <v>46274</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9765,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9808,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9818,14 +9803,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44998</v>
+        <v>46274</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9839,11 +9824,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9886,7 +9871,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9896,14 +9881,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45160</v>
+        <v>46274</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9915,8 +9900,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9959,7 +9949,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9973,10 +9963,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45748</v>
+        <v>45769</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9990,11 +9980,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>14.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10037,7 +10027,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10051,10 +10041,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45071</v>
+        <v>45769</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10066,13 +10056,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>2.2</v>
+        <v>9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10115,7 +10100,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10129,10 +10114,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45627</v>
+        <v>45632</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10145,7 +10130,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10188,7 +10173,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10202,10 +10187,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45503</v>
+        <v>44764</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10218,7 +10203,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10261,7 +10246,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10275,10 +10260,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45439</v>
+        <v>44998</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10288,6 +10273,11 @@
       <c r="G121" t="inlineStr">
         <is>
           <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -10334,7 +10324,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10348,10 +10338,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45193</v>
+        <v>45785</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10363,8 +10353,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10407,7 +10402,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10421,10 +10416,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45769</v>
+        <v>45785</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10438,11 +10433,11 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>14.6</v>
+        <v>6.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10485,7 +10480,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10499,10 +10494,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45125</v>
+        <v>45627</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10514,13 +10509,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10563,7 +10553,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10577,10 +10567,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44974</v>
+        <v>45635</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10593,7 +10583,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10636,7 +10626,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10650,10 +10640,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45632</v>
+        <v>45548</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10666,7 +10656,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10709,7 +10699,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10723,10 +10713,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44998</v>
+        <v>45810</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10740,11 +10730,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6.9</v>
+        <v>22.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10787,7 +10777,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10797,14 +10787,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44764</v>
+        <v>45840</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10816,8 +10806,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10860,7 +10855,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10870,14 +10865,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45785</v>
+        <v>45840</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10895,7 +10890,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10938,7 +10933,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10948,14 +10943,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45785</v>
+        <v>45840</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10973,7 +10968,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>18</v>
+        <v>2.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11016,7 +11011,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11026,14 +11021,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45627</v>
+        <v>45846</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11045,8 +11040,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11089,7 +11089,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11103,10 +11103,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45635</v>
+        <v>45819</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11179,7 +11179,7 @@
         <v>45840</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45840</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45840</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45846</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>46010</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46128</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>46135</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>46258</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>46274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 29532-2022</t>
+          <t>A 9956-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44753</v>
+        <v>44621</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,17 +1553,22 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1578,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1594,486 +1599,481 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Ögonpyrola
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 29532-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44753</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>Backruta
 Hagfingersvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 1683-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Talltita</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 17889-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46122</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I13" t="n">
         <v>2.7</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Tallticka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 7385-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>44971</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>3.5</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bolmört
 Tibast</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 1683-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46034</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Talltita</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 9956-2022</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 15334-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45770</v>
+        <v>45019</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2102,14 +2102,19 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>16.4</v>
+        <v>27.3</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2143,42 +2148,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3553-2026</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2192,10 +2197,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46042</v>
+        <v>45770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2208,16 +2213,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>16.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2232,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2248,42 +2253,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 15334-2023</t>
+          <t>A 50226-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2293,14 +2298,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45019</v>
+        <v>45943</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,17 +2319,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>27.3</v>
+        <v>0.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2358,42 +2363,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58307-2024</t>
+          <t>A 3553-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2407,10 +2412,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45632</v>
+        <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2423,31 +2428,31 @@
         </is>
       </c>
       <c r="I18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2463,42 +2468,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 58307-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2508,14 +2513,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45943</v>
+        <v>45632</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2527,19 +2532,14 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 25053-2022</t>
+          <t>A 51936-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44729</v>
+        <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 25057-2022</t>
+          <t>A 25053-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 69104-2021</t>
+          <t>A 25057-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44530</v>
+        <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3669,13 +3669,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3718,7 +3713,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 68174-2021</t>
+          <t>A 69104-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3732,10 +3727,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44526</v>
+        <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3749,11 +3744,11 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3796,7 +3791,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 68174-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3810,10 +3805,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45193</v>
+        <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3825,8 +3820,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3869,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51936-2022</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3879,14 +3879,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44872</v>
+        <v>45236</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45439</v>
+        <v>44858</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.9</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45247</v>
+        <v>45071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,8 +4044,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4088,7 +4093,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4102,10 +4107,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46078</v>
+        <v>45071</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4119,11 +4124,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>18.6</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4166,7 +4171,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4180,10 +4185,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44919</v>
+        <v>45627</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4196,7 +4201,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4239,7 +4244,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4253,10 +4258,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44858</v>
+        <v>45771</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4268,8 +4273,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>16.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4312,7 +4322,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4326,10 +4336,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46093</v>
+        <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4341,8 +4351,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4385,7 +4400,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4399,10 +4414,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45566</v>
+        <v>44739</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4415,7 +4430,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4458,7 +4473,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4472,10 +4487,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45442</v>
+        <v>45548</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4488,7 +4503,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4531,7 +4546,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 49311-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4545,10 +4560,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45627</v>
+        <v>44861</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4561,7 +4576,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4604,7 +4619,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4618,10 +4633,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45274</v>
+        <v>45810</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4633,8 +4648,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>22.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4677,7 +4697,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4687,14 +4707,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45925</v>
+        <v>45840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4706,8 +4726,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4750,7 +4775,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4760,14 +4785,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46122</v>
+        <v>45840</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4785,7 +4810,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4828,7 +4853,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4838,14 +4863,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44974</v>
+        <v>45840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4857,8 +4882,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>8.5</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4901,7 +4931,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4915,10 +4945,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46128</v>
+        <v>45446</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4930,13 +4960,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4979,7 +5004,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4989,14 +5014,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46128</v>
+        <v>45846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5014,7 +5039,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8.699999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5057,7 +5082,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5067,14 +5092,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46128</v>
+        <v>45819</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5086,13 +5111,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5135,7 +5155,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5149,10 +5169,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46122</v>
+        <v>45925</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5164,13 +5184,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5213,7 +5228,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5227,10 +5242,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46134</v>
+        <v>45566</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5242,13 +5257,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>13.2</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5291,7 +5301,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5301,14 +5311,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45071</v>
+        <v>45635</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5320,13 +5330,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5369,7 +5374,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5383,10 +5388,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45071</v>
+        <v>44919</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5398,13 +5403,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46134</v>
+        <v>44994</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5478,11 +5478,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5525,7 +5525,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5535,14 +5535,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46135</v>
+        <v>44781</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5556,11 +5556,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>22.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5603,7 +5603,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44953</v>
+        <v>44746</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5632,8 +5632,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5676,7 +5681,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5690,10 +5695,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44998</v>
+        <v>45972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5705,13 +5710,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5754,7 +5754,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5764,14 +5764,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46140</v>
+        <v>45995</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5785,11 +5785,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5832,7 +5832,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45972</v>
+        <v>46077</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5861,8 +5861,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>5.4</v>
+        <v>19.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5905,7 +5910,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5919,10 +5924,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45503</v>
+        <v>46078</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5934,8 +5939,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>6</v>
+        <v>18.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5978,7 +5988,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5992,10 +6002,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45821</v>
+        <v>46077</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6009,11 +6019,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6056,7 +6066,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6070,10 +6080,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46094</v>
+        <v>45112</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6086,7 +6096,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6129,7 +6139,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6139,14 +6149,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45722</v>
+        <v>46010</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6164,7 +6174,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>11.5</v>
+        <v>3.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6207,7 +6217,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6221,10 +6231,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45112</v>
+        <v>45789</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6237,7 +6247,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6280,7 +6290,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6294,10 +6304,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46150</v>
+        <v>46093</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6307,11 +6317,6 @@
       <c r="G69" t="inlineStr">
         <is>
           <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -6358,7 +6363,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6372,10 +6377,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46150</v>
+        <v>45222</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6387,13 +6392,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46150</v>
+        <v>45247</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6465,13 +6465,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6514,7 +6509,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6528,10 +6523,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46150</v>
+        <v>46122</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6549,7 +6544,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6592,7 +6587,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6606,10 +6601,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46150</v>
+        <v>46122</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6627,7 +6622,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>11.8</v>
+        <v>6.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6670,7 +6665,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6680,14 +6675,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45705</v>
+        <v>46128</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6701,11 +6696,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6748,7 +6743,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6762,10 +6757,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44739</v>
+        <v>46128</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6777,8 +6772,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6821,7 +6821,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6831,14 +6831,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45748</v>
+        <v>46128</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6899,7 +6899,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6909,14 +6909,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46010</v>
+        <v>46134</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>13.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6977,7 +6977,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6987,14 +6987,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45902</v>
+        <v>46135</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7008,11 +7008,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7055,7 +7055,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 49311-2022</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7069,10 +7069,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44861</v>
+        <v>45274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45789</v>
+        <v>46134</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7157,8 +7157,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7201,7 +7206,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7215,10 +7220,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46164</v>
+        <v>45627</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7231,7 +7236,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7274,7 +7279,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7288,10 +7293,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45071</v>
+        <v>45821</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7309,7 +7314,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7352,7 +7357,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7362,14 +7367,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46181</v>
+        <v>46140</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7387,7 +7392,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7430,7 +7435,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7444,10 +7449,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45236</v>
+        <v>46094</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7460,7 +7465,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7503,7 +7508,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7513,14 +7518,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45446</v>
+        <v>45705</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7532,8 +7537,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7576,7 +7586,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7590,10 +7600,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44746</v>
+        <v>45722</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7607,11 +7617,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>11.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7654,7 +7664,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7668,10 +7678,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44994</v>
+        <v>44481</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7683,13 +7693,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7732,7 +7737,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7742,14 +7747,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44781</v>
+        <v>45737</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7763,11 +7768,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>22.9</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7810,7 +7815,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7820,14 +7825,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45995</v>
+        <v>46150</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7841,11 +7846,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>11.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7888,7 +7893,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7902,10 +7907,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46077</v>
+        <v>46150</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7919,11 +7924,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7966,7 +7971,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7980,10 +7985,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46077</v>
+        <v>46150</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7997,11 +8002,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>19.5</v>
+        <v>4.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8044,7 +8049,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8058,10 +8063,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45835</v>
+        <v>46150</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8079,7 +8084,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8122,7 +8127,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8136,10 +8141,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46239</v>
+        <v>46150</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8151,8 +8156,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8195,7 +8205,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8205,14 +8215,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44481</v>
+        <v>45902</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8224,8 +8234,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8268,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 33191-2026</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8282,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46246</v>
+        <v>45769</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8299,11 +8314,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.6</v>
+        <v>10.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8346,7 +8361,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8360,10 +8375,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46246</v>
+        <v>45769</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8375,13 +8390,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>7.3</v>
+        <v>9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8424,7 +8434,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8438,10 +8448,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46246</v>
+        <v>46164</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8454,7 +8464,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8497,7 +8507,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8511,10 +8521,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45125</v>
+        <v>45442</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8526,13 +8536,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8575,7 +8580,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8589,10 +8594,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45627</v>
+        <v>44953</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8605,7 +8610,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>8</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8648,7 +8653,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8662,10 +8667,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45771</v>
+        <v>45762</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8683,7 +8688,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>16.8</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8726,7 +8731,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8740,10 +8745,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45627</v>
+        <v>44998</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8755,8 +8760,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8799,7 +8809,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8813,10 +8823,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45160</v>
+        <v>46181</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8828,8 +8838,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8872,7 +8887,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8886,10 +8901,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45635</v>
+        <v>45160</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8902,7 +8917,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8945,7 +8960,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8959,10 +8974,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45769</v>
+        <v>45748</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8976,11 +8991,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>10.1</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9023,7 +9038,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9033,14 +9048,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45737</v>
+        <v>45071</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9054,11 +9069,11 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9101,7 +9116,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9111,14 +9126,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46258</v>
+        <v>45835</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9136,7 +9151,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9179,7 +9194,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9193,10 +9208,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46213</v>
+        <v>45627</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9209,7 +9224,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9252,7 +9267,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9266,10 +9281,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45222</v>
+        <v>45503</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9282,7 +9297,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9325,7 +9340,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9339,10 +9354,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45128</v>
+        <v>46246</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9360,7 +9375,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9403,7 +9418,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9417,10 +9432,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46223</v>
+        <v>46246</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9432,13 +9447,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9481,7 +9491,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 33191-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9495,10 +9505,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45762</v>
+        <v>46246</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9516,7 +9526,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9559,7 +9569,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9573,10 +9583,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46268</v>
+        <v>45439</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9588,13 +9598,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>2.2</v>
+        <v>6.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9637,7 +9642,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9647,14 +9652,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46274</v>
+        <v>45193</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9666,13 +9671,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9715,7 +9715,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9725,14 +9725,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46274</v>
+        <v>46213</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9744,13 +9744,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9788,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9802,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46274</v>
+        <v>46258</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9828,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9871,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9881,14 +9876,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46274</v>
+        <v>45769</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9902,11 +9897,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.9</v>
+        <v>14.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9949,7 +9944,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9963,10 +9958,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45769</v>
+        <v>45125</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9980,11 +9975,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>14.6</v>
+        <v>3.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10027,7 +10022,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10041,10 +10036,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45769</v>
+        <v>46223</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10056,8 +10051,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10114,10 +10114,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45632</v>
+        <v>46268</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10129,8 +10129,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10173,7 +10178,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10187,10 +10192,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44764</v>
+        <v>44974</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10203,7 +10208,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10246,7 +10251,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10256,14 +10261,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44998</v>
+        <v>46274</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10277,11 +10282,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10324,7 +10329,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10334,14 +10339,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45785</v>
+        <v>46274</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10359,7 +10364,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>18</v>
+        <v>5.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10402,7 +10407,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10412,14 +10417,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45785</v>
+        <v>46274</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10437,7 +10442,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10480,7 +10485,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10490,14 +10495,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45627</v>
+        <v>46274</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10509,8 +10514,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10553,7 +10563,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10567,10 +10577,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45635</v>
+        <v>46239</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10583,7 +10593,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10626,7 +10636,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10640,10 +10650,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45548</v>
+        <v>45632</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10656,7 +10666,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10699,7 +10709,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10713,10 +10723,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45810</v>
+        <v>44998</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10730,11 +10740,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>22.6</v>
+        <v>6.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10777,7 +10787,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10787,14 +10797,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45840</v>
+        <v>44764</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10806,13 +10816,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10855,7 +10860,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10865,14 +10870,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45840</v>
+        <v>45785</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10890,7 +10895,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10933,7 +10938,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10943,14 +10948,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45840</v>
+        <v>45785</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10968,7 +10973,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.9</v>
+        <v>18</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11011,7 +11016,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11021,14 +11026,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45846</v>
+        <v>45627</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11040,13 +11045,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11089,7 +11089,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11103,10 +11103,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45819</v>
+        <v>45635</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11179,7 +11179,7 @@
         <v>45840</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45840</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45840</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45846</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>46010</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46128</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>46135</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>46258</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>46274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 9956-2022</t>
+          <t>A 1683-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1534,14 +1534,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44621</v>
+        <v>46034</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1559,22 +1559,22 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>29.2</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1599,481 +1599,481 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Skogsalm
+Talltita</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 17889-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 29532-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44753</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Backruta
+Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 7385-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44971</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Bolmört
+Tibast</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9956-2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Ögonpyrola
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 29532-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44753</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Backruta
-Hagfingersvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 1683-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46034</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Talltita</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17889-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 7385-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44971</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Tibast</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15334-2023</t>
+          <t>A 50226-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2083,14 +2083,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45019</v>
+        <v>45943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2104,17 +2104,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>27.3</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2148,42 +2148,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 15334-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45770</v>
+        <v>45019</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,14 +2212,19 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>16.4</v>
+        <v>27.3</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2253,42 +2258,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 58307-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2298,14 +2303,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45943</v>
+        <v>45632</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2317,19 +2322,14 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2363,35 +2363,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
         <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58307-2024</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45632</v>
+        <v>45770</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="I19" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45236</v>
+        <v>45439</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44858</v>
+        <v>45247</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45071</v>
+        <v>44858</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,13 +4044,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4093,7 +4088,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4107,10 +4102,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45071</v>
+        <v>44919</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4122,13 +4117,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4171,7 +4161,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4185,10 +4175,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45627</v>
+        <v>45566</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4201,7 +4191,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4244,7 +4234,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4258,10 +4248,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45771</v>
+        <v>45442</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4273,13 +4263,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>16.8</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4322,7 +4307,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4332,14 +4317,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45128</v>
+        <v>45995</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4353,11 +4338,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4400,7 +4385,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4414,10 +4399,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44739</v>
+        <v>44974</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4430,7 +4415,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4473,7 +4458,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4487,10 +4472,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45548</v>
+        <v>46077</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4502,8 +4487,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4546,7 +4536,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 49311-2022</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4560,10 +4550,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44861</v>
+        <v>46077</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4575,8 +4565,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>3.1</v>
+        <v>19.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4619,7 +4614,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4629,14 +4624,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45810</v>
+        <v>45071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4650,11 +4645,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>22.6</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4697,7 +4692,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4707,14 +4702,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45840</v>
+        <v>45071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4732,7 +4727,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4775,7 +4770,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4785,14 +4780,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45840</v>
+        <v>46078</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4806,11 +4801,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.2</v>
+        <v>18.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4870,7 +4865,7 @@
         <v>45840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4931,7 +4926,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4941,14 +4936,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45446</v>
+        <v>45840</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4960,8 +4955,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5004,7 +5004,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45846</v>
+        <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5082,7 +5082,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45819</v>
+        <v>46093</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5155,7 +5155,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5165,14 +5165,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45925</v>
+        <v>45846</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5184,8 +5184,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5228,7 +5233,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5242,10 +5247,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45566</v>
+        <v>45819</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5258,7 +5263,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5301,7 +5306,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5315,10 +5320,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45635</v>
+        <v>44998</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5330,8 +5335,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5374,7 +5384,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5388,10 +5398,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44919</v>
+        <v>45503</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5404,7 +5414,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5447,7 +5457,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5461,10 +5471,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44994</v>
+        <v>46122</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5478,11 +5488,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5525,7 +5535,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5539,10 +5549,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44781</v>
+        <v>46128</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5556,11 +5566,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>22.9</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5603,7 +5613,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5617,10 +5627,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44746</v>
+        <v>46128</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5634,11 +5644,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5681,7 +5691,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5691,14 +5701,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45972</v>
+        <v>46128</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5710,8 +5720,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5754,7 +5769,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5764,14 +5779,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45995</v>
+        <v>46122</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5785,11 +5800,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5832,7 +5847,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5846,10 +5861,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46077</v>
+        <v>46134</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5863,11 +5878,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>19.5</v>
+        <v>13.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5910,7 +5925,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5924,10 +5939,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46078</v>
+        <v>46134</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5941,11 +5956,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>18.6</v>
+        <v>4.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5988,7 +6003,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5998,14 +6013,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46077</v>
+        <v>46135</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6019,11 +6034,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.2</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6066,7 +6081,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6080,10 +6095,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45112</v>
+        <v>45722</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6095,8 +6110,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>11.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6139,7 +6159,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6149,14 +6169,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46010</v>
+        <v>45705</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6170,11 +6190,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6217,7 +6237,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6231,10 +6251,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45789</v>
+        <v>44739</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6247,7 +6267,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6290,7 +6310,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6304,10 +6324,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46093</v>
+        <v>45748</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6319,8 +6339,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6363,7 +6388,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 49311-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6377,10 +6402,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45222</v>
+        <v>44861</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6393,7 +6418,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6436,7 +6461,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6446,14 +6471,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45247</v>
+        <v>46140</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6465,8 +6490,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6509,7 +6539,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6523,10 +6553,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46122</v>
+        <v>45925</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6538,13 +6568,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6587,7 +6612,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6601,10 +6626,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46122</v>
+        <v>45071</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6622,7 +6647,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.9</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6665,7 +6690,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6679,10 +6704,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46128</v>
+        <v>45821</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6700,7 +6725,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6743,7 +6768,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6757,10 +6782,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46128</v>
+        <v>46094</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6772,13 +6797,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>8.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6821,7 +6841,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6831,14 +6851,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46128</v>
+        <v>46150</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6856,7 +6876,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6899,7 +6919,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6913,10 +6933,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46134</v>
+        <v>46150</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6934,7 +6954,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>13.2</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6977,7 +6997,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6987,14 +7007,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46135</v>
+        <v>46150</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7012,7 +7032,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>7.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7055,7 +7075,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7069,10 +7089,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45274</v>
+        <v>46150</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7084,8 +7104,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7128,7 +7153,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7142,10 +7167,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46134</v>
+        <v>46150</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7163,7 +7188,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.4</v>
+        <v>11.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7206,7 +7231,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7220,10 +7245,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45627</v>
+        <v>45236</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7236,7 +7261,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7279,7 +7304,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7293,10 +7318,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45821</v>
+        <v>45446</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7308,13 +7333,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7357,7 +7377,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7371,10 +7391,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46140</v>
+        <v>45902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7388,11 +7408,11 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7435,7 +7455,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7449,10 +7469,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46094</v>
+        <v>46164</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7465,7 +7485,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7508,7 +7528,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7518,14 +7538,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45705</v>
+        <v>44481</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7537,13 +7557,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.2</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7601,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7600,10 +7615,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45722</v>
+        <v>46181</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7621,7 +7636,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7664,7 +7679,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7678,10 +7693,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44481</v>
+        <v>45125</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7693,8 +7708,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7737,7 +7757,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7747,14 +7767,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45737</v>
+        <v>45627</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7766,13 +7786,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7815,7 +7830,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7829,10 +7844,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46150</v>
+        <v>45771</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7850,7 +7865,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>11.8</v>
+        <v>16.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7893,7 +7908,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7907,10 +7922,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46150</v>
+        <v>45160</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7922,13 +7937,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7971,7 +7981,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7985,10 +7995,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46150</v>
+        <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8006,7 +8016,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8049,7 +8059,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8063,10 +8073,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46150</v>
+        <v>45635</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8078,13 +8088,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8127,7 +8132,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8141,10 +8146,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46150</v>
+        <v>45769</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8158,11 +8163,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.5</v>
+        <v>10.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8205,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8215,14 +8220,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45902</v>
+        <v>45972</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8234,13 +8239,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8293,14 +8293,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45769</v>
+        <v>45737</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>10.1</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 33191-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45769</v>
+        <v>46246</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8390,8 +8390,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8434,7 +8439,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8448,10 +8453,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46164</v>
+        <v>46246</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8463,8 +8468,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8507,7 +8517,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8521,10 +8531,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45442</v>
+        <v>46246</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8537,7 +8547,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8580,7 +8590,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8594,10 +8604,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44953</v>
+        <v>45128</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8609,8 +8619,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8653,7 +8668,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8667,10 +8682,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45762</v>
+        <v>45193</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8682,13 +8697,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>8.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8731,7 +8741,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8741,14 +8751,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44998</v>
+        <v>46258</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8762,11 +8772,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8809,7 +8819,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8823,10 +8833,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46181</v>
+        <v>46213</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8838,13 +8848,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>7</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8887,7 +8892,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8901,10 +8906,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45160</v>
+        <v>46223</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8916,8 +8921,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8960,7 +8970,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8974,10 +8984,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45748</v>
+        <v>46268</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8991,11 +9001,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9038,7 +9048,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9052,10 +9062,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45071</v>
+        <v>45627</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9067,13 +9077,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9116,7 +9121,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9130,10 +9135,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45835</v>
+        <v>45274</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9145,13 +9150,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9194,7 +9194,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9204,14 +9204,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45627</v>
+        <v>46010</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9223,8 +9223,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9267,7 +9272,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9277,14 +9282,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45503</v>
+        <v>46274</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9296,8 +9301,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9340,7 +9350,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9350,14 +9360,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46246</v>
+        <v>46274</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9375,7 +9385,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9418,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9428,14 +9438,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46246</v>
+        <v>46274</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9447,8 +9457,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9491,7 +9506,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 33191-2026</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9501,14 +9516,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46246</v>
+        <v>46274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9526,7 +9541,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9569,7 +9584,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9583,10 +9598,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45439</v>
+        <v>45789</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9599,7 +9614,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6.9</v>
+        <v>2.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9642,7 +9657,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9656,10 +9671,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45193</v>
+        <v>44953</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9672,7 +9687,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>8.4</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9715,7 +9730,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9729,10 +9744,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46213</v>
+        <v>45112</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9745,7 +9760,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9788,7 +9803,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9798,14 +9813,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46258</v>
+        <v>46239</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9817,13 +9832,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9876,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9880,10 +9890,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45769</v>
+        <v>44746</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9897,11 +9907,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>14.6</v>
+        <v>2.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9944,7 +9954,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9958,10 +9968,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45125</v>
+        <v>44994</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9975,11 +9985,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10022,7 +10032,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10036,10 +10046,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46223</v>
+        <v>44781</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10053,11 +10063,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.4</v>
+        <v>22.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10100,7 +10110,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10114,10 +10124,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46268</v>
+        <v>45627</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10129,13 +10139,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10178,7 +10183,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10192,10 +10197,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44974</v>
+        <v>45222</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10208,7 +10213,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10251,7 +10256,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10261,14 +10266,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46274</v>
+        <v>45762</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10286,7 +10291,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10329,7 +10334,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10339,14 +10344,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46274</v>
+        <v>45769</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10360,11 +10365,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5.7</v>
+        <v>14.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10407,7 +10412,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10417,14 +10422,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46274</v>
+        <v>45769</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10436,13 +10441,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10485,7 +10485,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10495,14 +10495,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46274</v>
+        <v>45632</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10514,13 +10514,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10563,7 +10558,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10577,10 +10572,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46239</v>
+        <v>44764</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10593,7 +10588,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10636,7 +10631,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10650,10 +10645,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45632</v>
+        <v>44998</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10665,8 +10660,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10709,7 +10709,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10723,10 +10723,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44998</v>
+        <v>45785</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10740,11 +10740,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6.9</v>
+        <v>18</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10787,7 +10787,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10801,10 +10801,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44764</v>
+        <v>45785</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10816,8 +10816,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10860,7 +10865,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10874,10 +10879,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45785</v>
+        <v>45627</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10889,13 +10894,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>6.7</v>
+        <v>2.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10938,7 +10938,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10952,10 +10952,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45785</v>
+        <v>45635</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10967,13 +10967,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>18</v>
+        <v>2.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11016,7 +11011,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11030,10 +11025,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45627</v>
+        <v>45548</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11046,7 +11041,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11089,7 +11084,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11103,10 +11098,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45635</v>
+        <v>45810</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11118,8 +11113,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>22.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11179,7 +11179,7 @@
         <v>45840</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45840</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45840</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45846</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>46010</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46128</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>46135</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>46258</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>46274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1683-2026</t>
+          <t>A 9956-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1534,14 +1534,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46034</v>
+        <v>44621</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1559,22 +1559,22 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>29.2</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1599,481 +1599,481 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Ögonpyrola
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 29532-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44753</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Backruta
+Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 1683-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>Skogsalm
 Talltita</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 17889-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46122</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I13" t="n">
         <v>2.7</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Tallticka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 29532-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44753</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 7385-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44971</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Backruta
-Hagfingersvamp</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 7385-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44971</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bolmört
 Tibast</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 9956-2022</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2083,14 +2083,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45943</v>
+        <v>45770</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2102,13 +2102,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.1</v>
+        <v>16.4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2148,35 +2143,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
@@ -2200,7 +2195,7 @@
         <v>45019</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2293,7 +2288,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58307-2024</t>
+          <t>A 3553-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2307,10 +2302,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45632</v>
+        <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2323,31 +2318,31 @@
         </is>
       </c>
       <c r="I17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2363,42 +2358,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 3553-2026</t>
+          <t>A 50226-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2408,14 +2403,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46042</v>
+        <v>45943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,17 +2422,22 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2468,42 +2468,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 58307-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45770</v>
+        <v>45632</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>16.4</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45439</v>
+        <v>45236</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45247</v>
+        <v>44858</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44858</v>
+        <v>45071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,8 +4044,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4088,7 +4093,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4102,10 +4107,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44919</v>
+        <v>45071</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4117,8 +4122,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4161,7 +4171,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4175,10 +4185,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45566</v>
+        <v>45627</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4191,7 +4201,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4234,7 +4244,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4248,10 +4258,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45442</v>
+        <v>45128</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4263,8 +4273,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4307,7 +4322,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4317,14 +4332,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45995</v>
+        <v>45771</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4338,11 +4353,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>16.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4385,7 +4400,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4399,10 +4414,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44974</v>
+        <v>44739</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4415,7 +4430,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4458,7 +4473,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 49311-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4472,10 +4487,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46077</v>
+        <v>44861</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4487,13 +4502,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4536,7 +4546,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4550,10 +4560,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46077</v>
+        <v>45446</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4565,13 +4575,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>19.5</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4614,7 +4619,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4624,14 +4629,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45071</v>
+        <v>45566</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4643,13 +4648,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4692,7 +4692,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45071</v>
+        <v>45635</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4721,13 +4721,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4770,7 +4765,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4784,10 +4779,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46078</v>
+        <v>44919</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4799,13 +4794,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>18.6</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4848,7 +4838,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4858,14 +4848,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45840</v>
+        <v>45112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4877,13 +4867,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4926,7 +4911,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4936,14 +4921,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45840</v>
+        <v>45821</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4961,7 +4946,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5004,7 +4989,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5014,14 +4999,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45840</v>
+        <v>46140</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5039,7 +5024,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5082,7 +5067,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5096,10 +5081,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5112,7 +5097,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5155,7 +5140,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5165,14 +5150,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45846</v>
+        <v>45925</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5184,13 +5169,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5233,7 +5213,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5247,10 +5227,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45819</v>
+        <v>45222</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5263,7 +5243,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5306,7 +5286,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5320,10 +5300,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44998</v>
+        <v>45247</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5335,13 +5315,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5384,7 +5359,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5398,10 +5373,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45503</v>
+        <v>46150</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5413,8 +5388,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>11.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5457,7 +5437,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5471,10 +5451,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46122</v>
+        <v>46150</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5492,7 +5472,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5535,7 +5515,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5549,10 +5529,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46128</v>
+        <v>46150</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5570,7 +5550,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5613,7 +5593,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5627,10 +5607,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46128</v>
+        <v>46150</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5648,7 +5628,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5691,7 +5671,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5701,14 +5681,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46128</v>
+        <v>46150</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5726,7 +5706,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5769,7 +5749,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5783,10 +5763,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46122</v>
+        <v>45274</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5798,13 +5778,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5847,7 +5822,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5857,14 +5832,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46134</v>
+        <v>45902</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5878,11 +5853,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>13.2</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5925,7 +5900,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5939,10 +5914,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46134</v>
+        <v>45972</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5954,13 +5929,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6003,7 +5973,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6013,14 +5983,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46135</v>
+        <v>45627</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6032,13 +6002,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6081,7 +6046,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6091,14 +6056,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45722</v>
+        <v>45705</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6112,11 +6077,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>11.5</v>
+        <v>0.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6159,7 +6124,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6169,14 +6134,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45705</v>
+        <v>46164</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6188,13 +6153,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.2</v>
+        <v>6.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6237,7 +6197,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6251,10 +6211,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44739</v>
+        <v>45722</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6266,8 +6226,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>11.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6310,7 +6275,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6324,10 +6289,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45748</v>
+        <v>44481</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6339,13 +6304,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6388,7 +6348,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49311-2022</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6398,14 +6358,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44861</v>
+        <v>45737</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6417,8 +6377,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6461,7 +6426,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6471,14 +6436,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46140</v>
+        <v>46010</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6496,7 +6461,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6539,7 +6504,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6553,10 +6518,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45925</v>
+        <v>45789</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6569,7 +6534,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6612,7 +6577,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6626,10 +6591,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45071</v>
+        <v>45769</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6643,11 +6608,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.2</v>
+        <v>10.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6690,7 +6655,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6704,10 +6669,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45821</v>
+        <v>45769</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6719,13 +6684,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6768,7 +6728,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6782,10 +6742,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46094</v>
+        <v>45442</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6798,7 +6758,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6841,7 +6801,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6855,10 +6815,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46150</v>
+        <v>44953</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6870,13 +6830,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6919,7 +6874,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6933,10 +6888,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46150</v>
+        <v>45762</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6954,7 +6909,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6997,7 +6952,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7011,10 +6966,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46150</v>
+        <v>44994</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7028,11 +6983,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7.1</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7075,7 +7030,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7089,10 +7044,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46150</v>
+        <v>44781</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7106,11 +7061,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.5</v>
+        <v>22.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7153,7 +7108,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7167,10 +7122,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46150</v>
+        <v>44746</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7184,11 +7139,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>11.8</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7231,7 +7186,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7245,10 +7200,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45236</v>
+        <v>44998</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,8 +7215,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7304,7 +7264,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7318,10 +7278,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45446</v>
+        <v>46181</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7333,8 +7293,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7377,7 +7342,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7387,14 +7352,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45902</v>
+        <v>45995</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7412,7 +7377,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7455,7 +7420,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7469,10 +7434,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46164</v>
+        <v>46077</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7484,8 +7449,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7528,7 +7498,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7542,10 +7512,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44481</v>
+        <v>46078</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7557,8 +7527,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>18.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7601,7 +7576,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7615,10 +7590,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46181</v>
+        <v>46077</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7632,11 +7607,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7679,7 +7654,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7693,10 +7668,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45125</v>
+        <v>45160</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7708,13 +7683,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7757,7 +7727,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7771,10 +7741,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45627</v>
+        <v>45748</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7786,8 +7756,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7830,7 +7805,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7844,10 +7819,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45771</v>
+        <v>45071</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7865,7 +7840,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>16.8</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7908,7 +7883,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7922,10 +7897,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45160</v>
+        <v>46093</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7938,7 +7913,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7998,7 +7973,7 @@
         <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8059,7 +8034,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8073,10 +8048,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45635</v>
+        <v>45627</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8089,7 +8064,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8132,7 +8107,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8146,10 +8121,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45769</v>
+        <v>45503</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8161,13 +8136,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>10.1</v>
+        <v>6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8180,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8194,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45972</v>
+        <v>46122</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8239,8 +8209,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8258,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8293,14 +8268,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45737</v>
+        <v>45439</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8312,13 +8287,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>6.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8361,7 +8331,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33191-2026</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8375,10 +8345,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46246</v>
+        <v>46122</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8396,7 +8366,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.6</v>
+        <v>6.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8439,7 +8409,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8453,10 +8423,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46246</v>
+        <v>46128</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8474,7 +8444,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8517,7 +8487,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8531,10 +8501,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46246</v>
+        <v>46128</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8546,8 +8516,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8590,7 +8565,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8600,14 +8575,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45128</v>
+        <v>46128</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8625,7 +8600,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8668,7 +8643,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8682,10 +8657,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45193</v>
+        <v>46246</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8697,8 +8672,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8741,7 +8721,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8751,14 +8731,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46258</v>
+        <v>46134</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8776,7 +8756,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>6.6</v>
+        <v>13.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8819,7 +8799,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8833,10 +8813,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46213</v>
+        <v>46246</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8849,7 +8829,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8892,7 +8872,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8902,14 +8882,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46223</v>
+        <v>46135</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8923,11 +8903,11 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8970,7 +8950,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8984,10 +8964,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46268</v>
+        <v>46134</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9001,11 +8981,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9048,7 +9028,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9062,10 +9042,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45627</v>
+        <v>45193</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9078,7 +9058,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9121,7 +9101,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 33191-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9135,10 +9115,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45274</v>
+        <v>46246</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9150,8 +9130,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9194,7 +9179,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9204,14 +9189,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46010</v>
+        <v>45769</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9225,11 +9210,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.3</v>
+        <v>14.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9272,7 +9257,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9282,14 +9267,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46274</v>
+        <v>45125</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9307,7 +9292,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9350,7 +9335,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9360,14 +9345,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46274</v>
+        <v>46213</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9379,13 +9364,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9428,7 +9408,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9442,10 +9422,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46274</v>
+        <v>46258</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9463,7 +9443,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9506,7 +9486,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9516,14 +9496,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46274</v>
+        <v>44974</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9535,13 +9515,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>5.9</v>
+        <v>8.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9584,7 +9559,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9598,10 +9573,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45789</v>
+        <v>46223</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9613,8 +9588,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9657,7 +9637,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9671,10 +9651,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44953</v>
+        <v>46268</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9686,8 +9666,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9730,7 +9715,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9740,14 +9725,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45112</v>
+        <v>46274</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9759,8 +9744,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9803,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9813,14 +9803,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46239</v>
+        <v>46274</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9832,8 +9822,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9876,7 +9871,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9886,14 +9881,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44746</v>
+        <v>46274</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9907,11 +9902,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9954,7 +9949,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9964,14 +9959,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44994</v>
+        <v>46274</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9985,11 +9980,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.6</v>
+        <v>5.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10032,7 +10027,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10046,10 +10041,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44781</v>
+        <v>45632</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10061,13 +10056,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>22.9</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10110,7 +10100,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10124,10 +10114,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45627</v>
+        <v>44998</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10139,8 +10129,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>4.6</v>
+        <v>6.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10183,7 +10178,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10197,10 +10192,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45222</v>
+        <v>44764</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10213,7 +10208,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10256,7 +10251,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10270,10 +10265,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45762</v>
+        <v>45785</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10291,7 +10286,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>6.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10334,7 +10329,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10348,10 +10343,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45769</v>
+        <v>45785</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10365,11 +10360,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>14.6</v>
+        <v>18</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10412,7 +10407,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10426,10 +10421,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45769</v>
+        <v>45627</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10442,7 +10437,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>9</v>
+        <v>2.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10485,7 +10480,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10499,10 +10494,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45632</v>
+        <v>45635</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10515,7 +10510,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10558,7 +10553,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10572,10 +10567,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44764</v>
+        <v>46239</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10588,7 +10583,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10631,7 +10626,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10645,10 +10640,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44998</v>
+        <v>45548</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10660,13 +10655,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10709,7 +10699,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10723,10 +10713,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45785</v>
+        <v>45810</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10740,11 +10730,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>18</v>
+        <v>22.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10787,7 +10777,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10797,14 +10787,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45785</v>
+        <v>45840</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10822,7 +10812,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>6.7</v>
+        <v>2.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10865,7 +10855,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10875,14 +10865,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45627</v>
+        <v>45840</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10894,8 +10884,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10938,7 +10933,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10948,14 +10943,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45635</v>
+        <v>45840</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10967,8 +10962,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11011,7 +11011,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11021,14 +11021,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45548</v>
+        <v>45846</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11040,8 +11040,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11084,7 +11089,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11098,10 +11103,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45810</v>
+        <v>45819</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11113,13 +11118,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>22.6</v>
+        <v>2.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11179,7 +11179,7 @@
         <v>45840</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45840</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45840</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45846</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>46010</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46128</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>46135</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>46258</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>46274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>44621</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>44753</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46122</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45770</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45019</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45632</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45236</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44858</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45071</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45627</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45128</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45771</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>44739</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>44861</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45446</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45566</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>45635</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>44919</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>45112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>45821</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>46140</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>46094</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>45925</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>45222</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>45247</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>46150</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>46150</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>46150</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>46150</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>46150</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>45274</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>45902</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>45972</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>45627</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>45705</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>46164</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>45722</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44481</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>45737</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>46010</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>45789</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>45769</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>45769</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45442</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44953</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45762</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44994</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44781</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44746</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44998</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>46181</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>45995</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>46077</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>46078</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>46077</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>45160</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45748</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45071</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>46093</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45627</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45503</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>46122</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>45439</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>46122</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>46128</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>46128</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>46128</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>46246</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>46134</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>46246</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>46135</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>46134</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>45193</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>46246</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>45769</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45125</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>46213</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>46258</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44974</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>46223</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>46268</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>46274</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>46274</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>46274</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>46274</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45632</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>44998</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>44764</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>45785</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>45785</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45627</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45635</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>46239</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>45548</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>45810</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>45840</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45840</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>45840</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>45846</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45819</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45840</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45840</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45840</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45846</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>46010</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46128</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>46135</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>46258</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>46274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE141"/>
+  <dimension ref="A1:AE143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>44621</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>44753</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46122</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45770</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45019</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45632</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45236</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44858</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45071</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45627</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45128</v>
+        <v>45771</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>16.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45771</v>
+        <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>16.8</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4417,7 +4417,7 @@
         <v>44739</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>44861</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45446</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45566</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45635</v>
+        <v>44919</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4765,7 +4765,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44919</v>
+        <v>45635</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45112</v>
+        <v>46134</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4867,8 +4867,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4928,7 +4933,7 @@
         <v>45821</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4989,7 +4994,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4999,14 +5004,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46140</v>
+        <v>45925</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5018,13 +5023,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46094</v>
+        <v>45112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5150,14 +5150,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45925</v>
+        <v>46140</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5169,8 +5169,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5213,7 +5218,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5227,10 +5232,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45222</v>
+        <v>46094</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5243,7 +5248,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5286,7 +5291,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5300,10 +5305,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45247</v>
+        <v>46150</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5315,8 +5320,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>11.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5359,7 +5369,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5376,7 +5386,7 @@
         <v>46150</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5394,7 +5404,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>11.8</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5437,7 +5447,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5454,7 +5464,7 @@
         <v>46150</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5472,7 +5482,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5515,7 +5525,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5532,7 +5542,7 @@
         <v>46150</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5550,7 +5560,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5593,7 +5603,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5610,7 +5620,7 @@
         <v>46150</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5628,7 +5638,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7.1</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5671,7 +5681,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5681,14 +5691,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46150</v>
+        <v>45902</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5702,11 +5712,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5749,7 +5759,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5763,10 +5773,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45274</v>
+        <v>45222</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5779,7 +5789,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5822,7 +5832,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5832,14 +5842,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45902</v>
+        <v>45247</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5851,13 +5861,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5917,7 +5922,7 @@
         <v>45972</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5973,7 +5978,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5987,10 +5992,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45627</v>
+        <v>46164</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6003,7 +6008,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6046,7 +6051,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6056,14 +6061,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45705</v>
+        <v>45274</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6075,13 +6080,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6124,7 +6124,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6134,14 +6134,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46164</v>
+        <v>46010</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6153,8 +6153,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6197,7 +6202,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6211,10 +6216,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45722</v>
+        <v>45789</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6226,13 +6231,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>11.5</v>
+        <v>2.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6275,7 +6275,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44481</v>
+        <v>46181</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6304,8 +6304,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6348,7 +6353,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6358,14 +6363,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45737</v>
+        <v>45627</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6377,13 +6382,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6426,7 +6426,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6436,14 +6436,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46010</v>
+        <v>45835</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6504,7 +6504,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6514,14 +6514,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45789</v>
+        <v>45705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6533,8 +6533,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6577,7 +6582,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6591,10 +6596,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45769</v>
+        <v>44994</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6608,11 +6613,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>10.1</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6655,7 +6660,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6669,10 +6674,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45769</v>
+        <v>44781</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6684,8 +6689,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>22.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6728,7 +6738,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6742,10 +6752,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45442</v>
+        <v>44746</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6757,8 +6767,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6801,7 +6816,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6815,10 +6830,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44953</v>
+        <v>45722</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6830,8 +6845,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>11.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6874,7 +6894,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6888,10 +6908,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45762</v>
+        <v>44481</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6903,13 +6923,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6952,7 +6967,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6962,14 +6977,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44994</v>
+        <v>45737</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6983,11 +6998,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7030,7 +7045,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7040,14 +7055,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44781</v>
+        <v>45995</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7065,7 +7080,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>22.9</v>
+        <v>2.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7108,7 +7123,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7122,10 +7137,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44746</v>
+        <v>46077</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7139,11 +7154,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.9</v>
+        <v>19.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7186,7 +7201,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7200,10 +7215,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44998</v>
+        <v>46078</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7217,11 +7232,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.7</v>
+        <v>18.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7264,7 +7279,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7278,10 +7293,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46181</v>
+        <v>46077</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7295,11 +7310,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7342,7 +7357,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7352,14 +7367,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45995</v>
+        <v>45769</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7373,11 +7388,11 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.9</v>
+        <v>10.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7420,7 +7435,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7434,10 +7449,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46077</v>
+        <v>46246</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7451,11 +7466,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>19.5</v>
+        <v>7.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7498,7 +7513,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7512,10 +7527,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7527,13 +7542,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>18.6</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7576,7 +7586,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7590,10 +7600,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46077</v>
+        <v>45769</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7605,13 +7615,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7654,7 +7659,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7668,10 +7673,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45160</v>
+        <v>46246</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7684,7 +7689,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7727,7 +7732,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 33191-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7741,10 +7746,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45748</v>
+        <v>46246</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7762,7 +7767,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7805,7 +7810,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7819,10 +7824,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45071</v>
+        <v>45442</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7834,13 +7839,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7883,7 +7883,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46093</v>
+        <v>44953</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45835</v>
+        <v>46122</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8034,7 +8034,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8048,10 +8048,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45627</v>
+        <v>45762</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8063,8 +8063,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8107,7 +8112,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8121,10 +8126,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45503</v>
+        <v>46122</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8136,8 +8141,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8180,7 +8190,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8194,10 +8204,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8215,7 +8225,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8258,7 +8268,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8272,10 +8282,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45439</v>
+        <v>46128</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8287,8 +8297,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>6.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8331,7 +8346,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8341,14 +8356,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8366,7 +8381,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8409,7 +8424,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8423,10 +8438,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46128</v>
+        <v>44998</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8440,11 +8455,11 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8487,7 +8502,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8501,10 +8516,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8522,7 +8537,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.699999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8565,7 +8580,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8579,10 +8594,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8600,7 +8615,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8643,7 +8658,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8657,10 +8672,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46246</v>
+        <v>45160</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8672,13 +8687,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8721,7 +8731,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8735,10 +8745,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46134</v>
+        <v>45748</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8756,7 +8766,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>13.2</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8799,7 +8809,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8813,10 +8823,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46246</v>
+        <v>45071</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8828,8 +8838,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8872,7 +8887,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8882,14 +8897,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46135</v>
+        <v>46213</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8901,13 +8916,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8950,7 +8960,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8960,14 +8970,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46134</v>
+        <v>46258</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8985,7 +8995,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9028,7 +9038,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9042,10 +9052,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45193</v>
+        <v>45627</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9058,7 +9068,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9101,7 +9111,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 33191-2026</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9115,10 +9125,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46246</v>
+        <v>45503</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9130,13 +9140,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9179,7 +9184,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9193,10 +9198,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45769</v>
+        <v>45439</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9208,13 +9213,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>14.6</v>
+        <v>6.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9257,7 +9257,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45125</v>
+        <v>46223</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9288,11 +9288,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9335,7 +9335,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46213</v>
+        <v>45193</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>8.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9408,7 +9408,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9418,14 +9418,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46258</v>
+        <v>46268</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9439,11 +9439,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9486,7 +9486,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9496,14 +9496,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44974</v>
+        <v>46274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9515,8 +9515,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>8.5</v>
+        <v>2.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9559,7 +9564,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9569,14 +9574,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46223</v>
+        <v>46274</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9590,11 +9595,11 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9637,7 +9642,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9647,14 +9652,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9668,11 +9673,11 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9715,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9732,7 +9737,7 @@
         <v>46274</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,7 +9755,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9798,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9803,14 +9808,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46274</v>
+        <v>45769</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9824,11 +9829,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.7</v>
+        <v>14.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9871,7 +9876,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9881,14 +9886,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46274</v>
+        <v>45125</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9906,7 +9911,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9949,7 +9954,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9959,14 +9964,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46274</v>
+        <v>46239</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9978,13 +9983,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10027,7 +10027,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10041,10 +10041,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45632</v>
+        <v>44974</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 38973-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10114,10 +10114,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44998</v>
+        <v>46286</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10129,13 +10129,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>6.9</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10178,7 +10173,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 39234-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10192,10 +10187,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44764</v>
+        <v>46287</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10208,7 +10203,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10251,7 +10246,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10265,10 +10260,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45785</v>
+        <v>45632</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10280,13 +10275,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10329,7 +10319,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10343,10 +10333,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45785</v>
+        <v>44998</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10360,11 +10350,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>18</v>
+        <v>6.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10407,7 +10397,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10421,10 +10411,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45627</v>
+        <v>44764</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10437,7 +10427,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10480,7 +10470,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10494,10 +10484,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45635</v>
+        <v>45785</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10509,8 +10499,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>2.1</v>
+        <v>6.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10553,7 +10548,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10567,10 +10562,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46239</v>
+        <v>45785</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10582,8 +10577,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10626,7 +10626,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10640,10 +10640,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45548</v>
+        <v>45627</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10699,7 +10699,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45810</v>
+        <v>45635</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10728,13 +10728,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>22.6</v>
+        <v>2.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10777,7 +10772,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10787,14 +10782,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45840</v>
+        <v>45548</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10806,13 +10801,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10855,7 +10845,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10865,14 +10855,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45840</v>
+        <v>45810</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10886,11 +10876,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.2</v>
+        <v>22.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10933,7 +10923,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10950,7 +10940,7 @@
         <v>45840</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10968,7 +10958,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11011,7 +11001,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11025,10 +11015,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45846</v>
+        <v>45840</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11046,7 +11036,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11089,7 +11079,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11099,14 +11089,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45819</v>
+        <v>45840</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11118,8 +11108,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11162,24 +11157,24 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S 2078-2025</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45840</v>
+        <v>45846</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11197,7 +11192,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11240,24 +11235,24 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S 2080-2025</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45840</v>
+        <v>45819</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11269,13 +11264,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11318,7 +11308,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S 2079-2025</t>
+          <t>S 2078-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11335,7 +11325,7 @@
         <v>45840</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11353,7 +11343,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11396,7 +11386,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S 2121-2025</t>
+          <t>S 2080-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11410,10 +11400,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45846</v>
+        <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11431,7 +11421,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11474,7 +11464,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S 3554-2025</t>
+          <t>S 2079-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11488,10 +11478,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46010</v>
+        <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11509,7 +11499,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11552,7 +11542,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S 1073-2026</t>
+          <t>S 2121-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11566,10 +11556,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46128</v>
+        <v>45846</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11587,7 +11577,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11630,7 +11620,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S 1143-2026</t>
+          <t>S 3554-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11644,10 +11634,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46135</v>
+        <v>46010</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11665,7 +11655,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11708,158 +11698,314 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
+          <t>S 1073-2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D140" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E140" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141" ht="15" customHeight="1">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>S 1143-2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D141" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="E141" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>2</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142" ht="15" customHeight="1">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>S 2213-2026</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D140" s="1" t="n">
+      <c r="D142" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="E140" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
+      <c r="E142" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I140" t="n">
+      <c r="I142" t="n">
         <v>6.6</v>
       </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>S 2358-2026</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D141" s="1" t="n">
+      <c r="D143" s="1" t="n">
         <v>46274</v>
       </c>
-      <c r="E141" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
+      <c r="E143" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I141" t="n">
+      <c r="I143" t="n">
         <v>2.9</v>
       </c>
-      <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" t="n">
-        <v>0</v>
-      </c>
-      <c r="U141" t="n">
-        <v>0</v>
-      </c>
-      <c r="V141" s="2" t="inlineStr"/>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 9956-2022</t>
+          <t>A 7385-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1534,14 +1534,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44621</v>
+        <v>44971</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,22 +1553,17 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1583,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1599,481 +1594,486 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Bolmört
+Tibast</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 29532-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44753</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Backruta
+Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 9956-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>Ögonpyrola
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 29532-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44753</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 1683-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Backruta
-Hagfingersvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 1683-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46034</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Talltita</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 17889-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>46122</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>2.7</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Tallticka</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 7385-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44971</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Tibast</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 15334-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45770</v>
+        <v>45019</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2102,14 +2102,19 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>16.4</v>
+        <v>27.3</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2143,42 +2148,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15334-2023</t>
+          <t>A 58307-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2192,10 +2197,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45019</v>
+        <v>45632</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2207,13 +2212,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>27.3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2253,42 +2253,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3553-2026</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46042</v>
+        <v>45770</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>16.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2358,35 +2358,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
         <v>45943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58307-2024</t>
+          <t>A 3553-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45632</v>
+        <v>46042</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,31 +2533,31 @@
         </is>
       </c>
       <c r="I19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 51936-2022</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3504,14 +3504,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44872</v>
+        <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3523,8 +3523,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>6.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3567,7 +3572,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 25053-2022</t>
+          <t>A 51936-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3581,10 +3586,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44729</v>
+        <v>44872</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3597,7 +3602,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3640,7 +3645,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 25057-2022</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3654,10 +3659,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44729</v>
+        <v>45785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3669,8 +3674,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3713,7 +3723,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 69104-2021</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3727,10 +3737,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44530</v>
+        <v>45785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3744,11 +3754,11 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3791,7 +3801,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 68174-2021</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3805,10 +3815,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44526</v>
+        <v>45722</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3822,11 +3832,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>11.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3869,7 +3879,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3879,14 +3889,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45236</v>
+        <v>45705</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3898,8 +3908,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>0.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3957,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 25053-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3952,14 +3967,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44858</v>
+        <v>44729</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3972,7 +3987,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4015,7 +4030,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 25057-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4025,14 +4040,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45071</v>
+        <v>44729</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,13 +4059,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4093,7 +4103,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 69104-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4107,10 +4117,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45071</v>
+        <v>44530</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4124,11 +4134,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4171,7 +4181,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 68174-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4185,10 +4195,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45627</v>
+        <v>44526</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4200,8 +4210,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4244,7 +4259,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4258,10 +4273,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45771</v>
+        <v>44739</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4273,13 +4288,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>16.8</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4322,7 +4332,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4336,10 +4346,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45128</v>
+        <v>45748</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4357,7 +4367,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4400,7 +4410,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4414,10 +4424,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44739</v>
+        <v>45627</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4430,7 +4440,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4490,7 +4500,7 @@
         <v>44861</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4546,7 +4556,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4560,10 +4570,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45446</v>
+        <v>45635</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4576,7 +4586,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4619,7 +4629,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4633,10 +4643,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45566</v>
+        <v>45071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4648,8 +4658,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4692,7 +4707,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4706,10 +4721,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44919</v>
+        <v>45548</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4722,7 +4737,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4765,7 +4780,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4779,10 +4794,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45635</v>
+        <v>45439</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4795,7 +4810,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4838,7 +4853,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4852,10 +4867,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46134</v>
+        <v>45236</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4867,13 +4882,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4916,7 +4926,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4930,10 +4940,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45821</v>
+        <v>45446</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4945,13 +4955,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4994,7 +4999,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5008,10 +5013,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45925</v>
+        <v>45247</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5067,7 +5072,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5081,10 +5086,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45112</v>
+        <v>44919</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5097,7 +5102,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5140,7 +5145,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5150,14 +5155,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46140</v>
+        <v>44858</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5169,13 +5174,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46094</v>
+        <v>45566</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46150</v>
+        <v>45925</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5320,13 +5320,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>11.8</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5369,7 +5364,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5383,10 +5378,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46150</v>
+        <v>45810</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5400,11 +5395,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>22.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5447,7 +5442,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5461,10 +5456,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46150</v>
+        <v>44481</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5476,13 +5471,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5525,7 +5515,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5539,10 +5529,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46150</v>
+        <v>45442</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5554,13 +5544,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>7.1</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5603,7 +5588,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5617,10 +5602,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46150</v>
+        <v>45125</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5638,7 +5623,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5681,7 +5666,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5691,14 +5676,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45902</v>
+        <v>45627</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5710,13 +5695,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5759,7 +5739,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5773,10 +5753,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45222</v>
+        <v>45771</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5788,8 +5768,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>16.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5832,7 +5817,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5846,10 +5831,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45247</v>
+        <v>45160</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5862,7 +5847,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5905,7 +5890,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5919,10 +5904,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45972</v>
+        <v>44974</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5935,7 +5920,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.4</v>
+        <v>8.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5978,7 +5963,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5992,10 +5977,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46164</v>
+        <v>45635</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6008,7 +5993,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6051,7 +6036,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6061,14 +6046,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45274</v>
+        <v>45071</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6080,8 +6065,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6124,7 +6114,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6134,14 +6124,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46010</v>
+        <v>45071</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6159,7 +6149,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6202,7 +6192,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6216,10 +6206,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45789</v>
+        <v>45769</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6231,8 +6221,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.7</v>
+        <v>10.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6275,7 +6270,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6285,14 +6280,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46181</v>
+        <v>45737</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6306,11 +6301,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6353,7 +6348,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6367,10 +6362,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45627</v>
+        <v>45972</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6383,7 +6378,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6426,7 +6421,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6440,10 +6435,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45835</v>
+        <v>44998</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6457,11 +6452,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6504,7 +6499,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6514,14 +6509,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45705</v>
+        <v>45503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6533,13 +6528,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6582,7 +6572,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6596,10 +6586,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44994</v>
+        <v>45128</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6613,11 +6603,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6660,7 +6650,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6674,10 +6664,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44781</v>
+        <v>45193</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6689,13 +6679,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>22.9</v>
+        <v>8.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6738,7 +6723,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6748,14 +6733,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44746</v>
+        <v>45840</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6769,11 +6754,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6816,7 +6801,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6826,14 +6811,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45722</v>
+        <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6851,7 +6836,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6894,7 +6879,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6904,14 +6889,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44481</v>
+        <v>46010</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6923,8 +6908,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6967,7 +6957,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6977,14 +6967,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45737</v>
+        <v>45840</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6998,11 +6988,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7045,7 +7035,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7055,14 +7045,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45995</v>
+        <v>45789</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7074,13 +7064,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7123,7 +7108,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 38973-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7137,10 +7122,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46077</v>
+        <v>46286</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7152,13 +7137,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>19.5</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7201,7 +7181,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7215,10 +7195,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46078</v>
+        <v>45627</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7230,13 +7210,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>18.6</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7279,7 +7254,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7293,10 +7268,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46077</v>
+        <v>45274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7308,13 +7283,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>6.2</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7357,7 +7327,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7371,10 +7341,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45769</v>
+        <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7388,11 +7358,11 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>10.1</v>
+        <v>2.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7435,7 +7405,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7449,10 +7419,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46246</v>
+        <v>44994</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7466,11 +7436,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7483,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7527,10 +7497,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46093</v>
+        <v>44781</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7542,8 +7512,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>22.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7561,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7596,14 +7571,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45769</v>
+        <v>45995</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7615,8 +7590,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7639,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 33191-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7676,7 +7656,7 @@
         <v>46246</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7688,8 +7668,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7732,7 +7717,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 33191-2026</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7746,10 +7731,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46246</v>
+        <v>44953</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7761,13 +7746,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7810,7 +7790,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7824,10 +7804,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45442</v>
+        <v>46077</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7839,8 +7819,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7883,7 +7868,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7897,10 +7882,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44953</v>
+        <v>46246</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7912,8 +7897,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7956,7 +7946,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7970,10 +7960,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46122</v>
+        <v>46077</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7987,11 +7977,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>19.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8034,7 +8024,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8048,10 +8038,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45762</v>
+        <v>46078</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8065,11 +8055,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>18.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8112,7 +8102,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 39234-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8126,10 +8116,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46122</v>
+        <v>46287</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8141,13 +8131,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>6.9</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8190,7 +8175,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8204,10 +8189,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46128</v>
+        <v>46246</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8219,13 +8204,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8268,7 +8248,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8278,14 +8258,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46128</v>
+        <v>45846</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8303,7 +8283,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>8.699999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8346,7 +8326,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8356,14 +8336,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46128</v>
+        <v>46093</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8375,13 +8355,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8424,7 +8399,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8438,10 +8413,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44998</v>
+        <v>45819</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8453,13 +8428,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8502,7 +8472,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8516,10 +8486,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46134</v>
+        <v>45112</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8531,13 +8501,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>13.2</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8580,7 +8545,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8590,14 +8555,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46135</v>
+        <v>46122</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8615,7 +8580,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8658,7 +8623,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8672,10 +8637,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45160</v>
+        <v>46128</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8687,8 +8652,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8731,7 +8701,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8745,10 +8715,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45748</v>
+        <v>46128</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8766,7 +8736,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8809,7 +8779,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8819,14 +8789,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45071</v>
+        <v>46128</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8844,7 +8814,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8887,7 +8857,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8901,10 +8871,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46213</v>
+        <v>46122</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8916,8 +8886,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8960,7 +8935,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8970,14 +8945,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46258</v>
+        <v>46134</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8995,7 +8970,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6.6</v>
+        <v>13.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9038,7 +9013,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9052,10 +9027,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45627</v>
+        <v>46134</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9067,8 +9042,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9111,7 +9091,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9121,14 +9101,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45503</v>
+        <v>46135</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9140,8 +9120,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9184,7 +9169,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9198,10 +9183,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45439</v>
+        <v>45627</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9214,7 +9199,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6.9</v>
+        <v>4.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9257,7 +9242,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9271,10 +9256,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46223</v>
+        <v>45222</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9286,13 +9271,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9335,7 +9315,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9345,14 +9325,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45193</v>
+        <v>46140</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9364,8 +9344,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9408,7 +9393,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9422,10 +9407,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46268</v>
+        <v>45762</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9439,11 +9424,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9486,7 +9471,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9496,14 +9481,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46274</v>
+        <v>45769</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9517,11 +9502,11 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.9</v>
+        <v>14.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9564,7 +9549,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9574,14 +9559,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46274</v>
+        <v>45821</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9599,7 +9584,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9642,7 +9627,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9652,14 +9637,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46274</v>
+        <v>46094</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9671,13 +9656,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9720,7 +9700,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9730,14 +9710,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46274</v>
+        <v>45769</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9749,13 +9729,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9798,7 +9773,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9812,10 +9787,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45769</v>
+        <v>46150</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9829,11 +9804,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>14.6</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9876,7 +9851,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9890,10 +9865,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45125</v>
+        <v>46150</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9911,7 +9886,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9954,7 +9929,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9968,10 +9943,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46239</v>
+        <v>46150</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9983,8 +9958,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>7.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10027,7 +10007,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10041,10 +10021,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44974</v>
+        <v>46150</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10056,8 +10036,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10100,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 38973-2026</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10114,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46286</v>
+        <v>46150</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10129,8 +10114,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10173,7 +10163,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 39234-2026</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10187,10 +10177,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46287</v>
+        <v>45632</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10203,7 +10193,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10246,7 +10236,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10260,10 +10250,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45632</v>
+        <v>44764</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10276,7 +10266,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10319,7 +10309,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10329,14 +10319,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44998</v>
+        <v>45902</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10350,11 +10340,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6.9</v>
+        <v>1.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10397,7 +10387,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10411,10 +10401,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44764</v>
+        <v>46164</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10427,7 +10417,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10470,7 +10460,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10484,10 +10474,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45785</v>
+        <v>46181</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10505,7 +10495,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10548,7 +10538,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10562,10 +10552,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45785</v>
+        <v>45835</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10583,7 +10573,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10626,7 +10616,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10636,14 +10626,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45627</v>
+        <v>46258</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10655,8 +10645,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10699,7 +10694,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10713,10 +10708,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45635</v>
+        <v>46213</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10729,7 +10724,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10772,7 +10767,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10786,10 +10781,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45548</v>
+        <v>46223</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10801,8 +10796,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10845,7 +10845,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10859,10 +10859,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45810</v>
+        <v>46268</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10876,11 +10876,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>22.6</v>
+        <v>2.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10937,10 +10937,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45840</v>
+        <v>46274</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11001,7 +11001,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11015,10 +11015,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45840</v>
+        <v>46274</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11079,7 +11079,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11093,10 +11093,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45840</v>
+        <v>46274</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45846</v>
+        <v>46274</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11235,7 +11235,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11249,10 +11249,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45819</v>
+        <v>46239</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11325,7 +11325,7 @@
         <v>45840</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>45846</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>46010</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>46128</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46135</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>46258</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>46274</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 7385-2023</t>
+          <t>A 9956-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1534,14 +1534,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44971</v>
+        <v>44621</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,17 +1553,22 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1578,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1594,486 +1599,481 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Ögonpyrola
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 29532-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44753</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Backruta
+Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 1683-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Talltita</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17889-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 7385-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44971</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Bolmört
 Tibast</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 29532-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44753</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Backruta
-Hagfingersvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 9956-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 1683-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46034</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Talltita</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 17889-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15334-2023</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45019</v>
+        <v>45770</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2102,19 +2102,14 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>27.3</v>
+        <v>16.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2148,42 +2143,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 58307-2024</t>
+          <t>A 15334-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2197,10 +2192,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45632</v>
+        <v>45019</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,8 +2207,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>27.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2253,42 +2253,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 3553-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45770</v>
+        <v>46042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2318,17 +2318,17 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>16.4</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2358,35 +2358,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
         <v>45943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 3553-2026</t>
+          <t>A 58307-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46042</v>
+        <v>45632</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,16 +2533,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 51936-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3504,14 +3504,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44998</v>
+        <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3523,13 +3523,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>6.9</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3572,7 +3567,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 51936-2022</t>
+          <t>A 25053-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3586,10 +3581,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44872</v>
+        <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3602,7 +3597,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3645,7 +3640,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 25057-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3659,10 +3654,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45785</v>
+        <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3674,13 +3669,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3723,7 +3713,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 69104-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3737,10 +3727,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45785</v>
+        <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3754,11 +3744,11 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3801,7 +3791,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 68174-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3815,10 +3805,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45722</v>
+        <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3832,11 +3822,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>11.5</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3879,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3889,14 +3879,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45705</v>
+        <v>45236</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3908,13 +3898,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.2</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3957,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 25053-2022</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3967,14 +3952,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44729</v>
+        <v>44858</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3987,7 +3972,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4030,7 +4015,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 25057-2022</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4040,14 +4025,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44729</v>
+        <v>45071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4059,8 +4044,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4103,7 +4093,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 69104-2021</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4117,10 +4107,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44530</v>
+        <v>45071</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4134,11 +4124,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4181,7 +4171,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 68174-2021</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4195,10 +4185,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44526</v>
+        <v>45627</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4210,13 +4200,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4259,7 +4244,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4273,10 +4258,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44739</v>
+        <v>45771</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4288,8 +4273,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>16.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4332,7 +4322,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4346,10 +4336,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45748</v>
+        <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4367,7 +4357,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4410,7 +4400,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4424,10 +4414,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45627</v>
+        <v>44739</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4440,7 +4430,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4500,7 +4490,7 @@
         <v>44861</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4556,7 +4546,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4570,10 +4560,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45635</v>
+        <v>45446</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4586,7 +4576,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4629,7 +4619,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4643,10 +4633,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45071</v>
+        <v>45566</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4658,13 +4648,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4707,7 +4692,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4721,10 +4706,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45548</v>
+        <v>45635</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4737,7 +4722,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4780,7 +4765,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4790,14 +4775,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45439</v>
+        <v>46135</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4809,8 +4794,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>6.9</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4853,7 +4843,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4867,10 +4857,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45236</v>
+        <v>44919</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4883,7 +4873,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4926,7 +4916,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4940,10 +4930,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45446</v>
+        <v>46134</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4955,8 +4945,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4999,7 +4994,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5013,10 +5008,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45247</v>
+        <v>45925</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5072,7 +5067,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5086,10 +5081,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44919</v>
+        <v>45112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5102,7 +5097,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5145,7 +5140,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5159,10 +5154,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44858</v>
+        <v>45222</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5175,7 +5170,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5218,7 +5213,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5232,10 +5227,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45566</v>
+        <v>45821</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5247,8 +5242,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45925</v>
+        <v>45247</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5374,14 +5374,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45810</v>
+        <v>46140</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5395,11 +5395,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>22.6</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5442,7 +5442,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44481</v>
+        <v>46094</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5515,7 +5515,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45442</v>
+        <v>45972</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45125</v>
+        <v>45274</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5617,13 +5617,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5666,7 +5661,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5680,10 +5675,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45627</v>
+        <v>46150</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5695,8 +5690,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>11.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5753,10 +5753,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45771</v>
+        <v>46150</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>16.8</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45160</v>
+        <v>46150</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5846,8 +5846,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5890,7 +5895,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5904,10 +5909,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44974</v>
+        <v>46150</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5919,8 +5924,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5963,7 +5973,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5977,10 +5987,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45635</v>
+        <v>46150</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5992,8 +6002,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6036,7 +6051,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6050,10 +6065,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45071</v>
+        <v>45902</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6067,11 +6082,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6114,7 +6129,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6124,14 +6139,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45071</v>
+        <v>46010</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6149,7 +6164,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6192,7 +6207,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6206,10 +6221,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45769</v>
+        <v>45627</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6221,13 +6236,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>10.1</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6270,7 +6280,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6280,14 +6290,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45737</v>
+        <v>45789</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6299,13 +6309,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6348,7 +6353,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6362,10 +6367,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45972</v>
+        <v>46164</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6378,7 +6383,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6421,7 +6426,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6431,14 +6436,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44998</v>
+        <v>45705</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6452,11 +6457,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6499,7 +6504,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6513,10 +6518,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45503</v>
+        <v>45722</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6528,8 +6533,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6572,7 +6582,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6586,10 +6596,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45128</v>
+        <v>44481</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6601,13 +6611,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6650,7 +6655,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6660,14 +6665,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45193</v>
+        <v>45737</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6679,8 +6684,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>8.4</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6723,7 +6733,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6733,14 +6743,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45840</v>
+        <v>44994</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6754,11 +6764,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6801,7 +6811,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6811,14 +6821,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45840</v>
+        <v>44781</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6832,11 +6842,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.2</v>
+        <v>22.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6879,7 +6889,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6889,14 +6899,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46010</v>
+        <v>44746</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6910,11 +6920,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6957,7 +6967,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6971,10 +6981,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45840</v>
+        <v>45995</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6988,7 +6998,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -7035,7 +7045,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7049,10 +7059,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45789</v>
+        <v>45769</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7064,8 +7074,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>2.7</v>
+        <v>10.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7108,7 +7123,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38973-2026</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7122,10 +7137,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46286</v>
+        <v>46077</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7137,8 +7152,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>19.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7181,7 +7201,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7195,10 +7215,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45627</v>
+        <v>46078</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7210,8 +7230,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>18.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7254,7 +7279,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7268,10 +7293,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45274</v>
+        <v>46077</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7283,8 +7308,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>6.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7327,7 +7357,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7341,10 +7371,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44746</v>
+        <v>45769</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7356,13 +7386,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.9</v>
+        <v>9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7405,7 +7430,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7419,10 +7444,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44994</v>
+        <v>46093</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7434,13 +7459,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7483,7 +7503,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7497,10 +7517,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44781</v>
+        <v>45442</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7512,13 +7532,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>22.9</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7561,7 +7576,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7571,14 +7586,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45995</v>
+        <v>44953</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7590,13 +7605,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7639,7 +7649,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33191-2026</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7653,10 +7663,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46246</v>
+        <v>46181</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7674,7 +7684,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7717,7 +7727,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7731,10 +7741,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44953</v>
+        <v>45762</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7746,8 +7756,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7790,7 +7805,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7804,10 +7819,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46077</v>
+        <v>46122</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7821,11 +7836,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.2</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7868,7 +7883,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7882,10 +7897,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46246</v>
+        <v>44998</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7899,11 +7914,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.3</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7946,7 +7961,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7960,10 +7975,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46077</v>
+        <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7977,11 +7992,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>19.5</v>
+        <v>5.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8024,7 +8039,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8038,10 +8053,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46078</v>
+        <v>46122</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8055,11 +8070,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>18.6</v>
+        <v>6.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8102,7 +8117,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 39234-2026</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8116,10 +8131,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46287</v>
+        <v>46128</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8131,8 +8146,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8175,7 +8195,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8189,10 +8209,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46246</v>
+        <v>46128</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8204,8 +8224,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8248,7 +8273,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8262,10 +8287,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45846</v>
+        <v>46128</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8283,7 +8308,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8326,7 +8351,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8340,10 +8365,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46093</v>
+        <v>45160</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8356,7 +8381,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8399,7 +8424,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8413,10 +8438,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45819</v>
+        <v>46134</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8428,8 +8453,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>2.7</v>
+        <v>13.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8472,7 +8502,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8486,10 +8516,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45112</v>
+        <v>45748</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8501,8 +8531,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8545,7 +8580,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8559,10 +8594,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46122</v>
+        <v>45071</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8580,7 +8615,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8623,7 +8658,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8637,10 +8672,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46128</v>
+        <v>45627</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8652,13 +8687,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8701,7 +8731,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8715,10 +8745,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46128</v>
+        <v>45503</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8730,13 +8760,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>8.699999999999999</v>
+        <v>6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8779,7 +8804,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8789,14 +8814,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46128</v>
+        <v>45439</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8808,13 +8833,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8857,7 +8877,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8871,10 +8891,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46122</v>
+        <v>46213</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8886,13 +8906,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8935,7 +8950,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8949,10 +8964,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46134</v>
+        <v>45193</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8964,13 +8979,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>13.2</v>
+        <v>8.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9013,7 +9023,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9023,14 +9033,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46134</v>
+        <v>46258</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9048,7 +9058,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9091,7 +9101,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9101,14 +9111,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46135</v>
+        <v>45769</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9122,11 +9132,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>14.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9169,7 +9179,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9183,10 +9193,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45627</v>
+        <v>45125</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9198,8 +9208,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9242,7 +9257,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9256,10 +9271,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45222</v>
+        <v>46223</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9271,8 +9286,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9315,7 +9335,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9325,14 +9345,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46140</v>
+        <v>46268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9346,11 +9366,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9393,7 +9413,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9403,14 +9423,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45762</v>
+        <v>46274</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9428,7 +9448,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9471,7 +9491,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9481,14 +9501,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45769</v>
+        <v>46274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9502,11 +9522,11 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>14.6</v>
+        <v>5.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9549,7 +9569,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9559,14 +9579,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45821</v>
+        <v>46274</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9584,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9627,7 +9647,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9637,14 +9657,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46094</v>
+        <v>46274</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9656,8 +9676,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9700,7 +9725,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9714,10 +9739,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45769</v>
+        <v>44974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9730,7 +9755,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9773,7 +9798,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9787,10 +9812,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46150</v>
+        <v>46239</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9802,13 +9827,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9851,7 +9871,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9865,10 +9885,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46150</v>
+        <v>45632</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9880,13 +9900,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9929,7 +9944,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9943,10 +9958,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46150</v>
+        <v>44998</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9960,11 +9975,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10007,7 +10022,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10021,10 +10036,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46150</v>
+        <v>44764</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10036,13 +10051,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10095,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10109,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46150</v>
+        <v>45785</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10120,7 +10130,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>11.8</v>
+        <v>6.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10163,7 +10173,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10177,10 +10187,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45632</v>
+        <v>45785</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10192,8 +10202,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>18</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10236,7 +10251,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10250,10 +10265,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44764</v>
+        <v>45627</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10266,7 +10281,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10309,7 +10324,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 38973-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10319,14 +10334,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45902</v>
+        <v>46286</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10336,11 +10351,6 @@
       <c r="G122" t="inlineStr">
         <is>
           <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -10387,7 +10397,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10401,10 +10411,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46164</v>
+        <v>45635</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10417,7 +10427,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10460,7 +10470,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10474,10 +10484,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46181</v>
+        <v>46246</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10489,13 +10499,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10538,7 +10543,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 33191-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10552,10 +10557,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45835</v>
+        <v>46246</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10573,7 +10578,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10616,7 +10621,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10626,14 +10631,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46258</v>
+        <v>46246</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10651,7 +10656,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10694,7 +10699,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10708,10 +10713,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46213</v>
+        <v>45548</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10724,7 +10729,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10767,7 +10772,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 39234-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10781,10 +10786,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46223</v>
+        <v>46287</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10796,13 +10801,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10845,7 +10845,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10859,10 +10859,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46268</v>
+        <v>45810</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10876,11 +10876,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.2</v>
+        <v>22.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10937,10 +10937,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46274</v>
+        <v>45840</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11001,7 +11001,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11015,10 +11015,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46274</v>
+        <v>45840</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11079,7 +11079,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11093,10 +11093,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46274</v>
+        <v>45840</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46274</v>
+        <v>45846</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11235,7 +11235,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11249,10 +11249,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46239</v>
+        <v>45819</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11325,7 +11325,7 @@
         <v>45840</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>45846</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>46010</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>46128</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46135</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>46258</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>46274</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE143"/>
+  <dimension ref="A1:AE144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 9956-2022</t>
+          <t>A 1683-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1534,14 +1534,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44621</v>
+        <v>46034</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1559,22 +1559,22 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>29.2</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1599,481 +1599,481 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Skogsalm
+Talltita</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 17889-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 7385-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44971</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Bolmört
+Tibast</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 29532-2022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44753</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Backruta
+Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9956-2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Ögonpyrola
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 29532-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44753</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Backruta
-Hagfingersvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 1683-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46034</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Talltita</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17889-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 7385-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44971</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Tibast</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 50226-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2083,14 +2083,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45770</v>
+        <v>45943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2102,8 +2102,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>16.4</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2143,35 +2148,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
     </row>
@@ -2195,7 +2200,7 @@
         <v>45019</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2288,7 +2293,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3553-2026</t>
+          <t>A 58307-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2302,10 +2307,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46042</v>
+        <v>45632</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2318,16 +2323,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2342,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2358,42 +2363,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 3553-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2403,14 +2408,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45943</v>
+        <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2422,23 +2427,18 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2468,42 +2468,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58307-2024</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45632</v>
+        <v>45770</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="I19" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45236</v>
+        <v>45439</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44858</v>
+        <v>45247</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45071</v>
+        <v>45789</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,13 +4044,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4093,7 +4088,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4107,10 +4102,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45071</v>
+        <v>45548</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4122,13 +4117,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4171,7 +4161,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4185,10 +4175,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45627</v>
+        <v>44919</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4201,7 +4191,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4244,7 +4234,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4258,10 +4248,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45771</v>
+        <v>44858</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4273,13 +4263,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>16.8</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4322,7 +4307,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4336,10 +4321,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45128</v>
+        <v>45566</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4351,13 +4336,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4400,7 +4380,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4414,10 +4394,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44739</v>
+        <v>45442</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4430,7 +4410,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4473,7 +4453,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49311-2022</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4487,10 +4467,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44861</v>
+        <v>44746</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4502,8 +4482,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4546,7 +4531,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4560,10 +4545,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45446</v>
+        <v>44994</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4575,8 +4560,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4619,7 +4609,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4633,10 +4623,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45566</v>
+        <v>44781</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4648,8 +4638,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>22.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4692,7 +4687,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4702,14 +4697,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45635</v>
+        <v>45995</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4721,8 +4716,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4765,7 +4765,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4775,14 +4775,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46135</v>
+        <v>45925</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4794,13 +4794,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4843,7 +4838,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4857,10 +4852,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44919</v>
+        <v>46077</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4872,8 +4867,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4916,7 +4916,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46134</v>
+        <v>46077</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4947,11 +4947,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45925</v>
+        <v>46078</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5023,8 +5023,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>18.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5067,7 +5072,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5081,10 +5086,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45112</v>
+        <v>44974</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5097,7 +5102,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5140,7 +5145,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5154,10 +5159,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45222</v>
+        <v>45810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5169,8 +5174,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>22.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5213,7 +5223,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5223,14 +5233,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45821</v>
+        <v>45071</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5248,7 +5258,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5291,7 +5301,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5305,10 +5315,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45247</v>
+        <v>45071</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5320,8 +5330,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5364,7 +5379,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5374,14 +5389,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46140</v>
+        <v>46093</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5393,13 +5408,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5442,7 +5452,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5456,10 +5466,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46094</v>
+        <v>44998</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5471,8 +5481,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5515,7 +5530,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5529,10 +5544,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45972</v>
+        <v>46122</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5544,8 +5559,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5588,7 +5608,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5602,10 +5622,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45274</v>
+        <v>45503</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5618,7 +5638,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5661,7 +5681,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5675,10 +5695,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46150</v>
+        <v>45972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5690,13 +5710,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>11.8</v>
+        <v>5.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5739,7 +5754,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5753,10 +5768,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46150</v>
+        <v>46128</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5774,7 +5789,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5817,7 +5832,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5831,10 +5846,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46150</v>
+        <v>46128</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5852,7 +5867,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5895,7 +5910,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5905,14 +5920,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46150</v>
+        <v>46128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5930,7 +5945,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.1</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5973,7 +5988,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5987,10 +6002,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46150</v>
+        <v>46122</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6008,7 +6023,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>6.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6051,7 +6066,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6061,14 +6076,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45902</v>
+        <v>46134</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6082,11 +6097,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>13.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6129,7 +6144,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6139,14 +6154,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46010</v>
+        <v>46134</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6164,7 +6179,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6207,7 +6222,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6217,14 +6232,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45627</v>
+        <v>46135</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6236,8 +6251,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6280,7 +6300,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6294,10 +6314,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45789</v>
+        <v>45722</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6309,8 +6329,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.7</v>
+        <v>11.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6353,7 +6378,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6363,14 +6388,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46164</v>
+        <v>45705</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6382,8 +6407,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>6.8</v>
+        <v>0.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6426,7 +6456,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6440,10 +6470,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45705</v>
+        <v>46140</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6457,11 +6487,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6504,7 +6534,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6518,10 +6548,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45722</v>
+        <v>44739</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6533,13 +6563,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>11.5</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6582,7 +6607,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6592,14 +6617,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44481</v>
+        <v>46010</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6611,8 +6636,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6655,7 +6685,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6665,14 +6695,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45737</v>
+        <v>45748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6686,11 +6716,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6733,7 +6763,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 49311-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6747,10 +6777,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44994</v>
+        <v>44861</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6762,13 +6792,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6811,7 +6836,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6825,10 +6850,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44781</v>
+        <v>45821</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6842,11 +6867,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>22.9</v>
+        <v>6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6889,7 +6914,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6903,10 +6928,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44746</v>
+        <v>46094</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6918,13 +6943,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6967,7 +6987,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6977,14 +6997,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45995</v>
+        <v>45071</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6998,11 +7018,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7045,7 +7065,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7059,10 +7079,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45769</v>
+        <v>46150</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7076,11 +7096,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>10.1</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7123,7 +7143,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7137,10 +7157,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46077</v>
+        <v>46150</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7154,11 +7174,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>19.5</v>
+        <v>4.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7201,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7215,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46078</v>
+        <v>46150</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7232,11 +7252,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>18.6</v>
+        <v>7.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7279,7 +7299,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7293,10 +7313,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46077</v>
+        <v>46150</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7310,11 +7330,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7357,7 +7377,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7371,10 +7391,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45769</v>
+        <v>46150</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7386,8 +7406,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>9</v>
+        <v>11.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7430,7 +7455,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7440,14 +7465,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46093</v>
+        <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7459,8 +7484,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7503,7 +7533,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7517,10 +7547,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45442</v>
+        <v>45236</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7533,7 +7563,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7576,7 +7606,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7586,14 +7616,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44953</v>
+        <v>45840</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7605,8 +7635,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7649,7 +7684,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7659,14 +7694,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46181</v>
+        <v>45840</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7684,7 +7719,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7727,7 +7762,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7737,14 +7772,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45762</v>
+        <v>45840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7762,7 +7797,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7805,7 +7840,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7819,10 +7854,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46122</v>
+        <v>45446</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7834,13 +7869,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7883,7 +7913,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7893,14 +7923,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44998</v>
+        <v>45846</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7914,11 +7944,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7961,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7975,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45835</v>
+        <v>46164</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7990,13 +8020,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8039,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8053,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46122</v>
+        <v>45819</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8068,13 +8093,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>6.9</v>
+        <v>2.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8117,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8131,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46128</v>
+        <v>46181</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8152,7 +8172,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8195,7 +8215,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8209,10 +8229,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46128</v>
+        <v>44481</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8224,13 +8244,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>8.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8273,7 +8288,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8283,14 +8298,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46128</v>
+        <v>45125</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8308,7 +8323,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8351,7 +8366,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8365,10 +8380,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45160</v>
+        <v>45627</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8381,7 +8396,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8424,7 +8439,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8438,10 +8453,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46134</v>
+        <v>45835</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8459,7 +8474,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>13.2</v>
+        <v>5.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8502,7 +8517,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8516,10 +8531,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45748</v>
+        <v>45771</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8537,7 +8552,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>16.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8580,7 +8595,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8594,10 +8609,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45071</v>
+        <v>45160</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8609,13 +8624,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8658,7 +8668,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8672,10 +8682,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45627</v>
+        <v>45635</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8688,7 +8698,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8731,7 +8741,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8745,10 +8755,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45503</v>
+        <v>45769</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8760,8 +8770,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>6</v>
+        <v>10.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8804,7 +8819,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8814,14 +8829,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45439</v>
+        <v>45737</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8833,8 +8848,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8877,7 +8897,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8887,14 +8907,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46213</v>
+        <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8906,8 +8926,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8950,7 +8975,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8964,10 +8989,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45193</v>
+        <v>46213</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8980,7 +9005,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9023,7 +9048,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9033,14 +9058,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46258</v>
+        <v>45128</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9058,7 +9083,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9101,7 +9126,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9115,10 +9140,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45769</v>
+        <v>45193</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9130,13 +9155,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>14.6</v>
+        <v>8.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9179,7 +9199,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9193,10 +9213,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45125</v>
+        <v>46223</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9210,11 +9230,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9257,7 +9277,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9271,10 +9291,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46223</v>
+        <v>46268</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9288,11 +9308,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9335,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9345,14 +9365,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9366,11 +9386,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9430,7 +9450,7 @@
         <v>46274</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9508,7 +9528,7 @@
         <v>46274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9569,7 +9589,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9586,7 +9606,7 @@
         <v>46274</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9604,7 +9624,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9647,7 +9667,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9657,14 +9677,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46274</v>
+        <v>45627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9676,13 +9696,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9725,7 +9740,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9739,10 +9754,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44974</v>
+        <v>45274</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9755,7 +9770,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9815,7 +9830,7 @@
         <v>46239</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9871,7 +9886,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 38973-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9885,10 +9900,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45632</v>
+        <v>46286</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9901,7 +9916,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9944,7 +9959,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9958,10 +9973,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44998</v>
+        <v>44953</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9973,13 +9988,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10022,7 +10032,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 39234-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10036,10 +10046,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44764</v>
+        <v>46287</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10052,7 +10062,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10095,7 +10105,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10109,10 +10119,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45785</v>
+        <v>45112</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10124,13 +10134,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>6.7</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10173,7 +10178,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 33191-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10187,10 +10192,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45785</v>
+        <v>46246</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10208,7 +10213,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10251,7 +10256,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10265,10 +10270,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45627</v>
+        <v>46246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10280,8 +10285,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>2.7</v>
+        <v>7.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10324,7 +10334,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38973-2026</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10338,10 +10348,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46286</v>
+        <v>46246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10354,7 +10364,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10397,7 +10407,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 39897-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10411,10 +10421,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45635</v>
+        <v>46289</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10427,7 +10437,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10470,7 +10480,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10484,10 +10494,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46246</v>
+        <v>45627</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10500,7 +10510,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10543,7 +10553,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 33191-2026</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10557,10 +10567,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46246</v>
+        <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10572,13 +10582,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10621,7 +10626,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10635,10 +10640,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46246</v>
+        <v>45762</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10656,7 +10661,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>7.3</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10699,7 +10704,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10713,10 +10718,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45548</v>
+        <v>45769</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10728,8 +10733,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.6</v>
+        <v>14.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10772,7 +10782,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 39234-2026</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10786,10 +10796,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46287</v>
+        <v>45769</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10802,7 +10812,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10845,7 +10855,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10859,10 +10869,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45810</v>
+        <v>45632</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10874,13 +10884,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>22.6</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10923,7 +10928,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10933,14 +10938,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45840</v>
+        <v>44764</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10952,13 +10957,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11001,7 +11001,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11011,14 +11011,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45840</v>
+        <v>44998</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11032,11 +11032,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.2</v>
+        <v>6.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11079,7 +11079,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11089,14 +11089,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45840</v>
+        <v>45785</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.7</v>
+        <v>18</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11167,14 +11167,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45846</v>
+        <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11235,7 +11235,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11249,10 +11249,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45819</v>
+        <v>45627</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11308,24 +11308,24 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S 2078-2025</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45840</v>
+        <v>45635</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11337,13 +11337,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11386,7 +11381,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S 2080-2025</t>
+          <t>S 2078-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11403,7 +11398,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11421,7 +11416,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11464,7 +11459,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S 2079-2025</t>
+          <t>S 2080-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11481,7 +11476,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11499,7 +11494,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11542,7 +11537,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S 2121-2025</t>
+          <t>S 2079-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11556,10 +11551,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45846</v>
+        <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11577,7 +11572,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11620,7 +11615,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S 3554-2025</t>
+          <t>S 2121-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11634,10 +11629,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46010</v>
+        <v>45846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11655,7 +11650,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11698,7 +11693,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S 1073-2026</t>
+          <t>S 3554-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11712,10 +11707,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46128</v>
+        <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11733,7 +11728,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11776,7 +11771,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S 1143-2026</t>
+          <t>S 1073-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11790,10 +11785,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46135</v>
+        <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11811,7 +11806,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11854,158 +11849,236 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
+          <t>S 1143-2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D142" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="E142" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>2</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143" ht="15" customHeight="1">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>S 2213-2026</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D142" s="1" t="n">
+      <c r="D143" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="E142" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
+      <c r="E143" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I142" t="n">
+      <c r="I143" t="n">
         <v>6.6</v>
       </c>
-      <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>S 2358-2026</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D143" s="1" t="n">
+      <c r="D144" s="1" t="n">
         <v>46274</v>
       </c>
-      <c r="E143" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
+      <c r="E144" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I143" t="n">
+      <c r="I144" t="n">
         <v>2.9</v>
       </c>
-      <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" t="n">
-        <v>0</v>
-      </c>
-      <c r="U143" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" s="2" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46034</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>46122</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44971</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>44753</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>44621</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45019</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45632</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45770</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45439</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>45247</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45789</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>45548</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>44919</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>44858</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>45566</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>45442</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44746</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>44994</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44781</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45995</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45925</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>46077</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>46077</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>46078</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44974</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>45071</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45071</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>46093</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>44998</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>46122</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45503</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>45972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>46128</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>46128</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>46128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>46122</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>46134</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>46134</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>46135</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>45722</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45705</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>46140</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>44739</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>46010</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>45748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>44861</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>45821</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>46094</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45071</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>46150</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>46150</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>46150</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>46150</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>46150</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45236</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45840</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45840</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>45446</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         <v>45846</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>46164</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>45819</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>46181</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44481</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45125</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45627</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>45835</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45771</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>45160</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>45635</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45769</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>45737</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>46213</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>45128</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>45193</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>46223</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>46268</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>46274</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>46274</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>46274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>46274</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>45627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>45274</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>46239</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>46286</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44953</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>46287</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>45112</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>46246</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>46246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>46246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>46289</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45627</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>45762</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45769</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>45769</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45632</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44764</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>44998</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45785</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45627</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45635</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46274</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46034</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>46122</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44971</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>44753</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>44621</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45019</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45632</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45770</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45439</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>45247</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45789</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>45548</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>44919</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>44858</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>45566</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>45442</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44746</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>44994</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44781</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45995</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45925</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>46077</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>46077</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>46078</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44974</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>45071</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45071</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>46093</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>44998</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>46122</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45503</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>45972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>46128</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>46128</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>46128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>46122</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>46134</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>46134</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>46135</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>45722</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45705</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>46140</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>44739</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>46010</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>45748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>44861</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>45821</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>46094</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45071</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>46150</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>46150</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>46150</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>46150</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>46150</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45236</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45840</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45840</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>45446</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         <v>45846</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>46164</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>45819</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>46181</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44481</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45125</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45627</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>45835</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45771</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>45160</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>45635</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45769</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>45737</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>46213</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>45128</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>45193</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>46223</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>46268</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>46274</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>46274</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>46274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>46274</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>45627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>45274</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>46239</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>46286</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44953</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>46287</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>45112</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>46246</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>46246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>46246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>46289</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45627</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>45762</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45769</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>45769</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45632</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44764</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>44998</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45785</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45627</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45635</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46274</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1683-2026</t>
+          <t>A 9956-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1534,14 +1534,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46034</v>
+        <v>44621</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1559,22 +1559,22 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>29.2</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1599,481 +1599,481 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Ögonpyrola
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 29532-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44753</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Backruta
+Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 1683-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>Skogsalm
 Talltita</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 17889-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46122</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I13" t="n">
         <v>2.7</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Tallticka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 7385-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>44971</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>3.5</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bolmört
 Tibast</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 29532-2022</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44753</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Backruta
-Hagfingersvamp</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 9956-2022</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 15334-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2083,14 +2083,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45943</v>
+        <v>45019</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2104,17 +2104,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.1</v>
+        <v>27.3</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2148,42 +2148,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15334-2023</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45019</v>
+        <v>45770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,19 +2212,14 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>27.3</v>
+        <v>16.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2258,42 +2253,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58307-2024</t>
+          <t>A 50226-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2303,14 +2298,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45632</v>
+        <v>45943</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2322,14 +2317,19 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2363,35 +2363,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
         <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 58307-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45770</v>
+        <v>45632</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>16.4</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45439</v>
+        <v>45236</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45247</v>
+        <v>44858</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45789</v>
+        <v>45071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,8 +4044,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4088,7 +4093,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4102,10 +4107,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45548</v>
+        <v>45071</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4117,8 +4122,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4161,7 +4171,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4175,10 +4185,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44919</v>
+        <v>45627</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4191,7 +4201,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4234,7 +4244,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4248,10 +4258,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44858</v>
+        <v>45771</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4263,8 +4273,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>16.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4307,7 +4322,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4321,10 +4336,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45566</v>
+        <v>45635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4337,7 +4352,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4380,7 +4395,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4394,10 +4409,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45442</v>
+        <v>45128</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4409,8 +4424,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4453,7 +4473,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4467,10 +4487,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44746</v>
+        <v>45548</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4482,13 +4502,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4531,7 +4546,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4541,14 +4556,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44994</v>
+        <v>46010</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4562,11 +4577,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4609,7 +4624,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4623,10 +4638,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44781</v>
+        <v>45810</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4640,11 +4655,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4687,7 +4702,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4697,14 +4712,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45995</v>
+        <v>44739</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4716,13 +4731,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4765,7 +4775,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 49311-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4779,10 +4789,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45925</v>
+        <v>44861</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4795,7 +4805,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4838,7 +4848,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4852,10 +4862,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46077</v>
+        <v>45925</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4867,13 +4877,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>6.2</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4916,7 +4921,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4930,10 +4935,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46077</v>
+        <v>45789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4945,13 +4950,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>19.5</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5004,14 +5004,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46078</v>
+        <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5025,11 +5025,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>18.6</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5082,14 +5082,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44974</v>
+        <v>45840</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5101,8 +5101,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5145,7 +5150,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5155,14 +5160,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45810</v>
+        <v>45840</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5176,11 +5181,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>22.6</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5223,7 +5228,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5233,14 +5238,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45071</v>
+        <v>45846</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5258,7 +5263,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5301,7 +5306,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5315,10 +5320,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45071</v>
+        <v>45819</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5330,13 +5335,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5379,7 +5379,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46093</v>
+        <v>45446</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5452,7 +5452,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5466,10 +5466,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44998</v>
+        <v>45566</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5481,13 +5481,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5530,7 +5525,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5544,10 +5539,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46122</v>
+        <v>45972</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5559,13 +5554,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5608,7 +5598,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5622,10 +5612,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45503</v>
+        <v>45635</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5638,7 +5628,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5681,7 +5671,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5695,10 +5685,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45972</v>
+        <v>44919</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5711,7 +5701,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5754,7 +5744,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5768,10 +5758,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46128</v>
+        <v>44994</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5785,11 +5775,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5832,7 +5822,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5846,10 +5836,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46128</v>
+        <v>44781</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5863,11 +5853,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.699999999999999</v>
+        <v>22.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5910,7 +5900,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5920,14 +5910,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46128</v>
+        <v>44746</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5941,7 +5931,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -5988,7 +5978,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5998,14 +5988,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46122</v>
+        <v>45995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6019,11 +6009,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6066,7 +6056,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6080,10 +6070,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46134</v>
+        <v>46077</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6097,11 +6087,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>13.2</v>
+        <v>19.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6144,7 +6134,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6158,10 +6148,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6175,11 +6165,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>18.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6222,7 +6212,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6232,14 +6222,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46135</v>
+        <v>46077</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6253,11 +6243,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6300,7 +6290,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6314,10 +6304,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45722</v>
+        <v>45112</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6329,13 +6319,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>11.5</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6378,7 +6363,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6388,14 +6373,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45705</v>
+        <v>46093</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6407,13 +6392,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6456,7 +6436,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6466,14 +6446,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46140</v>
+        <v>45222</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6485,13 +6465,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6534,7 +6509,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6548,10 +6523,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44739</v>
+        <v>45247</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6564,7 +6539,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6607,7 +6582,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6617,14 +6592,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46010</v>
+        <v>46122</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6642,7 +6617,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6685,7 +6660,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6699,10 +6674,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45748</v>
+        <v>46122</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6720,7 +6695,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6763,7 +6738,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 49311-2022</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6777,10 +6752,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44861</v>
+        <v>46128</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6792,8 +6767,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6836,7 +6816,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6850,10 +6830,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45821</v>
+        <v>46128</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6871,7 +6851,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6914,7 +6894,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6924,14 +6904,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46094</v>
+        <v>46128</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6943,8 +6923,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6987,7 +6972,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7001,10 +6986,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45071</v>
+        <v>46134</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7022,7 +7007,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>13.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7065,7 +7050,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7075,14 +7060,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46150</v>
+        <v>46135</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7100,7 +7085,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7143,7 +7128,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7157,10 +7142,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46150</v>
+        <v>46134</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7178,7 +7163,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7221,7 +7206,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7220,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46150</v>
+        <v>45274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7250,13 +7235,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>7.1</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7299,7 +7279,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7313,10 +7293,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46150</v>
+        <v>45627</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,11 +7306,6 @@
       <c r="G82" t="inlineStr">
         <is>
           <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -7377,7 +7352,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7391,10 +7366,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46150</v>
+        <v>45821</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7412,7 +7387,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>11.8</v>
+        <v>6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7455,7 +7430,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7469,10 +7444,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45902</v>
+        <v>46140</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7486,11 +7461,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7533,7 +7508,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7547,10 +7522,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45236</v>
+        <v>46094</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7563,7 +7538,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7606,7 +7581,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7616,14 +7591,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45840</v>
+        <v>45705</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7637,11 +7612,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7684,7 +7659,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7694,14 +7669,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45840</v>
+        <v>45722</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7719,7 +7694,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7762,7 +7737,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7772,14 +7747,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45840</v>
+        <v>44481</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7791,13 +7766,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7840,7 +7810,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7850,14 +7820,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45446</v>
+        <v>45737</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7869,8 +7839,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7913,7 +7888,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7923,14 +7898,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45846</v>
+        <v>46150</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7948,7 +7923,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.4</v>
+        <v>11.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7966,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +7980,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46164</v>
+        <v>46150</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8020,8 +7995,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8044,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8058,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45819</v>
+        <v>46150</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8093,8 +8073,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8122,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8136,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46181</v>
+        <v>46150</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8172,7 +8157,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8215,7 +8200,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8229,10 +8214,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44481</v>
+        <v>46150</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8244,8 +8229,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8288,7 +8278,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8298,14 +8288,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45125</v>
+        <v>45902</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8319,11 +8309,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8366,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8380,10 +8370,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45627</v>
+        <v>45769</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8395,8 +8385,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>8</v>
+        <v>10.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8439,7 +8434,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8453,10 +8448,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45835</v>
+        <v>45769</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8468,13 +8463,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8517,7 +8507,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8531,10 +8521,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45771</v>
+        <v>46164</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8546,13 +8536,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8595,7 +8580,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8609,10 +8594,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45160</v>
+        <v>45442</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8625,7 +8610,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8668,7 +8653,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8682,10 +8667,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45635</v>
+        <v>44953</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8698,7 +8683,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8741,7 +8726,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8755,10 +8740,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45769</v>
+        <v>45762</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8772,11 +8757,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8819,7 +8804,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8829,14 +8814,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45737</v>
+        <v>44998</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8850,11 +8835,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8897,7 +8882,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8907,14 +8892,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46258</v>
+        <v>46181</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8932,7 +8917,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8975,7 +8960,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8989,10 +8974,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46213</v>
+        <v>45160</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9005,7 +8990,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9048,7 +9033,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9062,10 +9047,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45128</v>
+        <v>45748</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9083,7 +9068,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9126,7 +9111,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9140,10 +9125,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45193</v>
+        <v>45071</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9155,8 +9140,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9199,7 +9189,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9213,10 +9203,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46223</v>
+        <v>45835</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9230,11 +9220,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9277,7 +9267,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9291,10 +9281,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46268</v>
+        <v>45627</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9306,13 +9296,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9355,7 +9340,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9365,14 +9350,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46274</v>
+        <v>45503</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9384,13 +9369,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9433,7 +9413,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9443,14 +9423,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46274</v>
+        <v>45439</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9462,13 +9442,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9511,7 +9486,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9521,14 +9496,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46274</v>
+        <v>45193</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9540,13 +9515,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9589,7 +9559,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9599,14 +9569,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46274</v>
+        <v>46213</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9618,13 +9588,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>5.9</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9667,7 +9632,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9677,14 +9642,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45627</v>
+        <v>46258</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9696,8 +9661,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9740,7 +9710,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9754,10 +9724,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45274</v>
+        <v>45769</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9769,8 +9739,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>14.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9813,7 +9788,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9827,10 +9802,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46239</v>
+        <v>45125</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9842,8 +9817,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9886,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 38973-2026</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9900,10 +9880,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46286</v>
+        <v>46223</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9915,8 +9895,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9959,7 +9944,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9973,10 +9958,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44953</v>
+        <v>46268</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9988,8 +9973,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10032,7 +10022,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 39234-2026</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10046,10 +10036,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46287</v>
+        <v>44974</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10062,7 +10052,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.1</v>
+        <v>8.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10105,7 +10095,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10115,14 +10105,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45112</v>
+        <v>46274</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10134,8 +10124,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10178,7 +10173,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 33191-2026</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10188,14 +10183,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46246</v>
+        <v>46274</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10213,7 +10208,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10256,7 +10251,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10266,14 +10261,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46246</v>
+        <v>46274</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10291,7 +10286,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10334,7 +10329,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10344,14 +10339,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46246</v>
+        <v>46274</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10363,8 +10358,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 39897-2026</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10421,10 +10421,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46289</v>
+        <v>46239</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10480,7 +10480,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45627</v>
+        <v>45632</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10553,7 +10553,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10567,10 +10567,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45222</v>
+        <v>44998</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10582,8 +10582,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10626,7 +10631,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10640,10 +10645,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45762</v>
+        <v>44764</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10655,13 +10660,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10704,7 +10704,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45769</v>
+        <v>45785</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10735,11 +10735,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>14.6</v>
+        <v>6.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10782,7 +10782,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10796,10 +10796,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45769</v>
+        <v>45785</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10811,8 +10811,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10855,7 +10860,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10869,10 +10874,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45632</v>
+        <v>45627</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10885,7 +10890,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10928,7 +10933,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 38973-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10942,10 +10947,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44764</v>
+        <v>46286</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10958,7 +10963,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11001,7 +11006,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11015,10 +11020,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44998</v>
+        <v>46246</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11030,13 +11035,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>6.9</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11079,7 +11079,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 33191-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11093,10 +11093,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45785</v>
+        <v>46246</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45785</v>
+        <v>46246</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11235,7 +11235,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 39234-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11249,10 +11249,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45627</v>
+        <v>46287</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11308,7 +11308,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 39897-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11322,10 +11322,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45635</v>
+        <v>46289</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11398,7 +11398,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46274</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 9956-2022</t>
+          <t>A 29532-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44621</v>
+        <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,22 +1553,17 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1583,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1599,481 +1594,486 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Backruta
+Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 1683-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Talltita</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 7385-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44971</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Bolmört
+Tibast</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17889-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9956-2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Ögonpyrola
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 29532-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44753</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Backruta
-Hagfingersvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 1683-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46034</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Talltita</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17889-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 7385-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44971</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Tibast</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15334-2023</t>
+          <t>A 50226-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2083,14 +2083,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45019</v>
+        <v>45943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2104,17 +2104,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>27.3</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2148,42 +2148,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 15334-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45770</v>
+        <v>45019</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,14 +2212,19 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>16.4</v>
+        <v>27.3</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2253,42 +2258,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 58307-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2298,14 +2303,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45943</v>
+        <v>45632</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2317,19 +2322,14 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2363,35 +2363,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
         <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58307-2024</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45632</v>
+        <v>45770</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="I19" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 25053-2022</t>
+          <t>A 69104-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44729</v>
+        <v>44530</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3596,8 +3596,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3640,7 +3645,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 25057-2022</t>
+          <t>A 68174-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3654,10 +3659,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44729</v>
+        <v>44526</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3669,8 +3674,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3713,7 +3723,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 69104-2021</t>
+          <t>A 25053-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3723,14 +3733,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44530</v>
+        <v>44729</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3742,13 +3752,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3791,7 +3796,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 68174-2021</t>
+          <t>A 25057-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3805,10 +3810,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44526</v>
+        <v>44729</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3820,13 +3825,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3869,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45236</v>
+        <v>45439</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44858</v>
+        <v>45635</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45071</v>
+        <v>45789</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,13 +4044,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4093,7 +4088,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4107,10 +4102,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45071</v>
+        <v>45247</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4122,13 +4117,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4171,7 +4161,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4185,10 +4175,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45627</v>
+        <v>45548</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4201,7 +4191,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4244,7 +4234,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4258,10 +4248,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45771</v>
+        <v>44919</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4273,13 +4263,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>16.8</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4322,7 +4307,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4336,10 +4321,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45635</v>
+        <v>44858</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4352,7 +4337,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4395,7 +4380,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4409,10 +4394,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45128</v>
+        <v>45810</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4426,11 +4411,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>22.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4473,7 +4458,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4487,10 +4472,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45548</v>
+        <v>45566</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4503,7 +4488,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4546,7 +4531,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4556,14 +4541,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46010</v>
+        <v>45442</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4575,13 +4560,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4624,7 +4604,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4638,10 +4618,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45810</v>
+        <v>45925</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4653,13 +4633,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>22.6</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4702,7 +4677,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4712,14 +4687,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44739</v>
+        <v>45840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4731,8 +4706,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4775,7 +4755,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49311-2022</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4785,14 +4765,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44861</v>
+        <v>45840</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4804,8 +4784,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4848,7 +4833,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4862,10 +4847,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45925</v>
+        <v>44974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4878,7 +4863,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4921,7 +4906,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4931,14 +4916,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45789</v>
+        <v>45840</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4950,8 +4935,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4994,7 +4984,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5008,10 +4998,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45840</v>
+        <v>45846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5029,7 +5019,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5072,7 +5062,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5082,14 +5072,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45840</v>
+        <v>45071</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5107,7 +5097,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5150,7 +5140,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5160,14 +5150,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45840</v>
+        <v>45071</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5185,7 +5175,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5228,7 +5218,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5238,14 +5228,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45846</v>
+        <v>45819</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5257,13 +5247,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5306,7 +5291,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5320,10 +5305,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45819</v>
+        <v>44998</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5335,8 +5320,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5379,7 +5369,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5393,10 +5383,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45446</v>
+        <v>44746</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5408,8 +5398,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5452,7 +5447,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5466,10 +5461,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45566</v>
+        <v>44994</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5481,8 +5476,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5525,7 +5525,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45972</v>
+        <v>44781</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5554,8 +5554,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>5.4</v>
+        <v>22.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5598,7 +5603,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5612,10 +5617,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45635</v>
+        <v>45503</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5628,7 +5633,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5671,7 +5676,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5685,10 +5690,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44919</v>
+        <v>45972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5701,7 +5706,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5744,7 +5749,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5754,14 +5759,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44994</v>
+        <v>45995</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5779,7 +5784,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5822,7 +5827,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5836,10 +5841,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44781</v>
+        <v>46077</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5853,11 +5858,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>22.9</v>
+        <v>6.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5900,7 +5905,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5914,10 +5919,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44746</v>
+        <v>46077</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5931,11 +5936,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>19.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5978,7 +5983,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5988,14 +5993,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45995</v>
+        <v>46078</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6009,11 +6014,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>18.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6056,7 +6061,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46077</v>
+        <v>45722</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6087,11 +6092,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6134,7 +6139,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6144,14 +6149,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46078</v>
+        <v>45705</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6169,7 +6174,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>18.6</v>
+        <v>0.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6212,7 +6217,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6226,10 +6231,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46077</v>
+        <v>44739</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6241,13 +6246,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45112</v>
+        <v>46093</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6373,14 +6373,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46093</v>
+        <v>46010</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6392,8 +6392,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6436,7 +6441,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6450,10 +6455,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45222</v>
+        <v>45748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6465,8 +6470,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6509,7 +6519,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 49311-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6523,10 +6533,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45247</v>
+        <v>44861</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6539,7 +6549,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6582,7 +6592,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6596,10 +6606,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46122</v>
+        <v>45071</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6617,7 +6627,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6660,7 +6670,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6677,7 +6687,7 @@
         <v>46122</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6695,7 +6705,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.9</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6755,7 +6765,7 @@
         <v>46128</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6833,7 +6843,7 @@
         <v>46128</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6911,7 +6921,7 @@
         <v>46128</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6972,7 +6982,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6986,10 +6996,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46134</v>
+        <v>46122</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7007,7 +7017,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>13.2</v>
+        <v>6.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7050,7 +7060,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7060,14 +7070,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46135</v>
+        <v>45236</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7079,13 +7089,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7128,7 +7133,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7145,7 +7150,7 @@
         <v>46134</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7163,7 +7168,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.4</v>
+        <v>13.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7206,7 +7211,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7220,10 +7225,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45274</v>
+        <v>45446</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7236,7 +7241,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7279,7 +7284,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7293,10 +7298,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45627</v>
+        <v>46134</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7308,8 +7313,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7352,7 +7362,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7362,14 +7372,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45821</v>
+        <v>46135</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7387,7 +7397,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7447,7 +7457,7 @@
         <v>46140</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7508,7 +7518,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7522,10 +7532,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46094</v>
+        <v>44481</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7538,7 +7548,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7581,7 +7591,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7591,14 +7601,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45705</v>
+        <v>45125</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7612,11 +7622,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7669,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7673,10 +7683,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45722</v>
+        <v>45821</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7694,7 +7704,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7737,7 +7747,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7751,10 +7761,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44481</v>
+        <v>45627</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7767,7 +7777,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7810,7 +7820,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7820,14 +7830,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45737</v>
+        <v>46094</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7839,13 +7849,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7888,7 +7893,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7902,10 +7907,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46150</v>
+        <v>45771</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7923,7 +7928,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>11.8</v>
+        <v>16.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7966,7 +7971,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7980,10 +7985,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46150</v>
+        <v>45160</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7995,13 +8000,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8044,7 +8044,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8061,7 +8061,7 @@
         <v>46150</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8122,7 +8122,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8139,7 +8139,7 @@
         <v>46150</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8200,7 +8200,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8217,7 +8217,7 @@
         <v>46150</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.5</v>
+        <v>7.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8278,7 +8278,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8288,14 +8288,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45902</v>
+        <v>46150</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8309,11 +8309,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45769</v>
+        <v>46150</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8387,11 +8387,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>10.1</v>
+        <v>11.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45769</v>
+        <v>45635</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>9</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46164</v>
+        <v>45769</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8536,8 +8536,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>6.8</v>
+        <v>10.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8580,7 +8585,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8590,14 +8595,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45442</v>
+        <v>45737</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8609,8 +8614,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8653,7 +8663,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8663,14 +8673,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44953</v>
+        <v>45902</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8682,8 +8692,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8726,7 +8741,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8740,10 +8755,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45762</v>
+        <v>46164</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8755,13 +8770,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8804,7 +8814,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8818,10 +8828,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44998</v>
+        <v>45128</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8835,11 +8845,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8882,7 +8892,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8896,10 +8906,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46181</v>
+        <v>45193</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8911,13 +8921,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8960,7 +8965,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8974,10 +8979,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45160</v>
+        <v>46181</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8989,8 +8994,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9033,7 +9043,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9047,10 +9057,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45748</v>
+        <v>45835</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9068,7 +9078,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9111,7 +9121,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9125,10 +9135,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45071</v>
+        <v>45627</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9140,13 +9150,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9189,7 +9194,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9203,10 +9208,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45835</v>
+        <v>45274</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9218,13 +9223,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9267,7 +9267,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45627</v>
+        <v>44953</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9340,7 +9340,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9354,10 +9354,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45503</v>
+        <v>45112</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9413,7 +9413,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9423,14 +9423,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45439</v>
+        <v>46258</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9442,8 +9442,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9486,7 +9491,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9500,10 +9505,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45193</v>
+        <v>46213</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9516,7 +9521,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9559,7 +9564,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9573,10 +9578,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46213</v>
+        <v>46223</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9588,8 +9593,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9632,7 +9642,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9642,14 +9652,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46258</v>
+        <v>46268</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9663,11 +9673,11 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9710,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9720,14 +9730,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45769</v>
+        <v>46274</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9741,11 +9751,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>14.6</v>
+        <v>6.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9788,7 +9798,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9798,14 +9808,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45125</v>
+        <v>46274</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9823,7 +9833,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9876,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9876,14 +9886,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46223</v>
+        <v>46274</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9897,11 +9907,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9944,7 +9954,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9954,14 +9964,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9975,11 +9985,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10022,7 +10032,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10036,10 +10046,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44974</v>
+        <v>45627</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10052,7 +10062,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10095,7 +10105,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10105,14 +10115,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46274</v>
+        <v>45222</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10124,13 +10134,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10173,7 +10178,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10183,14 +10188,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46274</v>
+        <v>45762</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10208,7 +10213,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10251,7 +10256,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10261,14 +10266,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46274</v>
+        <v>46239</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10280,13 +10285,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10329,7 +10329,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 38973-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10339,14 +10339,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46274</v>
+        <v>46286</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10358,13 +10358,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10407,7 +10402,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10421,10 +10416,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46239</v>
+        <v>45769</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10436,8 +10431,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>14.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10480,7 +10480,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45632</v>
+        <v>45769</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10553,7 +10553,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 39234-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10567,10 +10567,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44998</v>
+        <v>46287</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10582,13 +10582,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>6.9</v>
+        <v>4.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10631,7 +10626,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10645,10 +10640,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44764</v>
+        <v>45632</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10661,7 +10656,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10704,7 +10699,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10718,10 +10713,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45785</v>
+        <v>44764</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10733,13 +10728,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10782,7 +10772,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 33191-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10796,10 +10786,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45785</v>
+        <v>46246</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10817,7 +10807,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10860,7 +10850,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10874,10 +10864,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45627</v>
+        <v>46246</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10889,8 +10879,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2.7</v>
+        <v>7.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10933,7 +10928,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 38973-2026</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10947,10 +10942,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46286</v>
+        <v>44998</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10962,8 +10957,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>6.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11023,7 +11023,7 @@
         <v>46246</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 33191-2026</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11093,10 +11093,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46246</v>
+        <v>45785</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 39897-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46246</v>
+        <v>46289</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11186,13 +11186,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11235,7 +11230,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 39234-2026</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11249,10 +11244,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46287</v>
+        <v>45785</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11264,8 +11259,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>4.1</v>
+        <v>6.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11308,7 +11308,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 39897-2026</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11322,10 +11322,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46289</v>
+        <v>45627</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11398,7 +11398,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46274</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 29532-2022</t>
+          <t>A 7385-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1534,14 +1534,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44753</v>
+        <v>44971</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1594,486 +1594,486 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Bolmört
+Tibast</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 9956-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Ögonpyrola
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 29532-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44753</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>Backruta
 Hagfingersvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 1683-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I13" t="n">
         <v>29.2</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Talltita</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 7385-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44971</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 17889-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Tibast</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17889-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Tallticka</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 9956-2022</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 15334-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2083,14 +2083,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45943</v>
+        <v>45019</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2104,17 +2104,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.1</v>
+        <v>27.3</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2148,42 +2148,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15334-2023</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45019</v>
+        <v>45770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,19 +2212,14 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>27.3</v>
+        <v>16.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2258,35 +2253,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
@@ -2310,7 +2305,7 @@
         <v>45632</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2398,7 +2393,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 3553-2026</t>
+          <t>A 50226-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2408,14 +2403,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46042</v>
+        <v>45943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,17 +2422,22 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2468,42 +2468,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 3553-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45770</v>
+        <v>46042</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>16.4</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30868-2022</t>
+          <t>A 74425-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3129,14 +3129,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44767</v>
+        <v>44564</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 74425-2021</t>
+          <t>A 29510-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44564</v>
+        <v>44753</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3221,8 +3221,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3265,7 +3270,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 29510-2022</t>
+          <t>A 29513-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3282,7 +3287,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3300,7 +3305,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3343,7 +3348,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29513-2022</t>
+          <t>A 30868-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3353,14 +3358,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44753</v>
+        <v>44767</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3372,13 +3377,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 69104-2021</t>
+          <t>A 25053-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44530</v>
+        <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3596,13 +3596,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3645,7 +3640,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 68174-2021</t>
+          <t>A 25057-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3659,10 +3654,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44526</v>
+        <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3674,13 +3669,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3723,7 +3713,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25053-2022</t>
+          <t>A 69104-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3733,14 +3723,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44729</v>
+        <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3752,8 +3742,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3796,7 +3791,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25057-2022</t>
+          <t>A 68174-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3810,10 +3805,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44729</v>
+        <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3825,8 +3820,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3869,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45439</v>
+        <v>45236</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45635</v>
+        <v>45769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3971,8 +3971,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>14.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4015,7 +4020,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4025,14 +4030,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45789</v>
+        <v>45705</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,8 +4049,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4088,7 +4098,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4102,10 +4112,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45247</v>
+        <v>45566</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4118,7 +4128,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4161,7 +4171,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4175,10 +4185,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45548</v>
+        <v>45125</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4190,8 +4200,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4234,7 +4249,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4248,10 +4263,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44919</v>
+        <v>45722</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4263,8 +4278,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>11.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4307,7 +4327,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4321,10 +4341,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44858</v>
+        <v>44481</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4337,7 +4357,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4380,7 +4400,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4394,10 +4414,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45810</v>
+        <v>44858</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4409,13 +4429,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>22.6</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4458,7 +4473,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4468,14 +4483,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45566</v>
+        <v>45737</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4487,8 +4502,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4531,7 +4551,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4545,10 +4565,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45442</v>
+        <v>45635</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4561,7 +4581,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4604,7 +4624,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4618,10 +4638,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45925</v>
+        <v>44919</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4634,7 +4654,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4677,7 +4697,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4687,14 +4707,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45840</v>
+        <v>45769</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4708,11 +4728,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>10.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4755,7 +4775,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4765,14 +4785,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45840</v>
+        <v>45627</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4784,13 +4804,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4833,7 +4848,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4843,14 +4858,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44974</v>
+        <v>45071</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4862,8 +4877,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4906,7 +4926,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4916,14 +4936,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45840</v>
+        <v>45071</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4941,7 +4961,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4984,7 +5004,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4994,14 +5014,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45846</v>
+        <v>45769</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5013,13 +5033,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5062,7 +5077,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5072,14 +5087,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45071</v>
+        <v>44974</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5091,13 +5106,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>8.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5140,7 +5150,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5154,10 +5164,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45071</v>
+        <v>45442</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5169,13 +5179,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5218,7 +5223,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5232,10 +5237,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45819</v>
+        <v>44953</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5248,7 +5253,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5291,7 +5296,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5305,10 +5310,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44998</v>
+        <v>45771</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5322,11 +5327,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.7</v>
+        <v>16.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5369,7 +5374,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5383,10 +5388,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44746</v>
+        <v>45762</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5400,11 +5405,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5447,7 +5452,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5461,10 +5466,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44994</v>
+        <v>45112</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5476,13 +5481,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5525,7 +5525,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44781</v>
+        <v>44998</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5556,11 +5556,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>22.9</v>
+        <v>3.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5603,7 +5603,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45503</v>
+        <v>45632</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45972</v>
+        <v>44998</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5705,8 +5705,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>5.4</v>
+        <v>6.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5749,7 +5754,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5759,14 +5764,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45995</v>
+        <v>45160</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5778,13 +5783,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5827,7 +5827,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5841,10 +5841,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46077</v>
+        <v>44764</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5856,13 +5856,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5905,7 +5900,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5919,10 +5914,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46077</v>
+        <v>45785</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5936,11 +5931,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>19.5</v>
+        <v>6.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5983,7 +5978,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5997,10 +5992,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46078</v>
+        <v>45785</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6014,11 +6009,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6061,7 +6056,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45722</v>
+        <v>45627</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6090,13 +6085,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>11.5</v>
+        <v>2.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6139,7 +6129,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6149,14 +6139,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45705</v>
+        <v>45222</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6168,13 +6158,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6217,7 +6202,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6231,10 +6216,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44739</v>
+        <v>45748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6246,8 +6231,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6290,7 +6280,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6304,10 +6294,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46093</v>
+        <v>45071</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6319,8 +6309,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6363,7 +6358,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6373,14 +6368,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46010</v>
+        <v>45635</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6392,13 +6387,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6441,7 +6431,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6455,10 +6445,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45748</v>
+        <v>45128</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6476,7 +6466,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6519,7 +6509,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49311-2022</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6533,10 +6523,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44861</v>
+        <v>45247</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6549,7 +6539,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6592,7 +6582,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6606,10 +6596,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45071</v>
+        <v>45548</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6621,13 +6611,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6670,7 +6655,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6684,10 +6669,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46122</v>
+        <v>44739</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6699,13 +6684,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6748,7 +6728,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6762,10 +6742,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46128</v>
+        <v>45627</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6777,13 +6757,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6826,7 +6801,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6840,10 +6815,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46128</v>
+        <v>45503</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6855,13 +6830,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>8.699999999999999</v>
+        <v>6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6904,7 +6874,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6914,14 +6884,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46128</v>
+        <v>45810</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6935,11 +6905,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>22.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6982,7 +6952,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 49311-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6996,10 +6966,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46122</v>
+        <v>44861</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7011,13 +6981,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>6.9</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7060,7 +7025,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7074,10 +7039,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45236</v>
+        <v>45439</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7090,7 +7055,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7133,7 +7098,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7147,10 +7112,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46134</v>
+        <v>45274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7162,13 +7127,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>13.2</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7211,7 +7171,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7225,10 +7185,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45446</v>
+        <v>45193</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7241,7 +7201,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>8.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7284,7 +7244,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7294,14 +7254,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46134</v>
+        <v>45840</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7319,7 +7279,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7362,7 +7322,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7376,10 +7336,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46135</v>
+        <v>45840</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7397,7 +7357,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7440,7 +7400,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7450,14 +7410,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46140</v>
+        <v>45840</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7475,7 +7435,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7518,7 +7478,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7528,14 +7488,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44481</v>
+        <v>45846</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7547,8 +7507,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7591,7 +7556,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7605,10 +7570,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45125</v>
+        <v>45819</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7620,13 +7585,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7669,7 +7629,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7683,10 +7643,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45821</v>
+        <v>45627</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7698,13 +7658,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7747,7 +7702,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7761,10 +7716,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45627</v>
+        <v>45446</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7777,7 +7732,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>8</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7820,7 +7775,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7834,10 +7789,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46094</v>
+        <v>45925</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7850,7 +7805,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7893,7 +7848,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7907,10 +7862,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45771</v>
+        <v>45972</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7922,13 +7877,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>16.8</v>
+        <v>5.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7971,7 +7921,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7981,14 +7931,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45160</v>
+        <v>46010</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8000,8 +7950,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8044,7 +7999,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8058,10 +8013,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46150</v>
+        <v>45789</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8073,13 +8028,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8122,7 +8072,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8136,10 +8086,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46150</v>
+        <v>44994</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8153,11 +8103,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8200,7 +8150,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8214,10 +8164,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46150</v>
+        <v>44781</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8231,11 +8181,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>7.1</v>
+        <v>22.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8278,7 +8228,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8292,10 +8242,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46150</v>
+        <v>44746</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8309,11 +8259,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8306,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8366,14 +8316,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46150</v>
+        <v>45995</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8387,11 +8337,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>11.8</v>
+        <v>2.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8434,7 +8384,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8448,10 +8398,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45635</v>
+        <v>46077</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8463,8 +8413,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>19.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8507,7 +8462,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8521,10 +8476,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45769</v>
+        <v>46078</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8542,7 +8497,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>10.1</v>
+        <v>18.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8585,7 +8540,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8595,14 +8550,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45737</v>
+        <v>46077</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8620,7 +8575,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8663,7 +8618,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8673,14 +8628,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45902</v>
+        <v>46093</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8692,13 +8647,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8741,7 +8691,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8755,10 +8705,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46164</v>
+        <v>46122</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8770,8 +8720,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8814,7 +8769,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8828,10 +8783,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45128</v>
+        <v>46122</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8849,7 +8804,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8892,7 +8847,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8906,10 +8861,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45193</v>
+        <v>46128</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8921,8 +8876,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8965,7 +8925,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8979,10 +8939,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46181</v>
+        <v>46128</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9000,7 +8960,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9043,7 +9003,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9053,14 +9013,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45835</v>
+        <v>46128</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9078,7 +9038,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9121,7 +9081,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9135,10 +9095,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45627</v>
+        <v>46134</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9150,8 +9110,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>3.5</v>
+        <v>13.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9194,7 +9159,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9204,14 +9169,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45274</v>
+        <v>46135</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9223,8 +9188,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9267,7 +9237,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9281,10 +9251,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44953</v>
+        <v>46134</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9296,8 +9266,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9340,7 +9315,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9354,10 +9329,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45112</v>
+        <v>45821</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9369,8 +9344,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9413,7 +9393,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9423,14 +9403,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46258</v>
+        <v>46140</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9448,7 +9428,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6.6</v>
+        <v>0.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9491,7 +9471,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9505,10 +9485,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46213</v>
+        <v>46094</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9521,7 +9501,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9564,7 +9544,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9578,10 +9558,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46223</v>
+        <v>46150</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9595,11 +9575,11 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.4</v>
+        <v>11.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9642,7 +9622,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9656,10 +9636,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46268</v>
+        <v>46150</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9673,11 +9653,11 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9720,7 +9700,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9730,14 +9710,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46274</v>
+        <v>46150</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9755,7 +9735,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9798,7 +9778,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9808,14 +9788,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46274</v>
+        <v>46150</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9833,7 +9813,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>7.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9876,7 +9856,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9886,14 +9866,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46274</v>
+        <v>46150</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9911,7 +9891,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9954,7 +9934,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9964,14 +9944,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46274</v>
+        <v>45902</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9985,11 +9965,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10032,7 +10012,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10046,10 +10026,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45627</v>
+        <v>46164</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10062,7 +10042,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10105,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10119,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45222</v>
+        <v>46181</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10134,8 +10114,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10178,7 +10163,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10192,10 +10177,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45762</v>
+        <v>45835</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10213,7 +10198,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10256,7 +10241,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10270,10 +10255,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46239</v>
+        <v>46213</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10286,7 +10271,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10329,7 +10314,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38973-2026</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10339,14 +10324,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46286</v>
+        <v>46258</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10358,8 +10343,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10402,7 +10392,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10416,10 +10406,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45769</v>
+        <v>46223</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10437,7 +10427,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>14.6</v>
+        <v>4.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10480,7 +10470,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10494,10 +10484,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45769</v>
+        <v>46268</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10509,8 +10499,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10553,7 +10548,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 39234-2026</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10563,14 +10558,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46287</v>
+        <v>46274</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10582,8 +10577,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10626,7 +10626,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10636,14 +10636,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45632</v>
+        <v>46274</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10655,8 +10655,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10699,7 +10704,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10709,14 +10714,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44764</v>
+        <v>46274</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10728,8 +10733,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10772,7 +10782,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 33191-2026</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10782,14 +10792,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46246</v>
+        <v>46274</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10807,7 +10817,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10850,7 +10860,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10864,10 +10874,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46246</v>
+        <v>46239</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10879,13 +10889,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>7.3</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10928,7 +10933,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 38973-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10942,10 +10947,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44998</v>
+        <v>46286</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10957,13 +10962,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>6.9</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11023,7 +11023,7 @@
         <v>46246</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 33191-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11093,10 +11093,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45785</v>
+        <v>46246</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 39897-2026</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46289</v>
+        <v>46246</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11186,8 +11186,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11230,7 +11235,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 39234-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11244,10 +11249,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45785</v>
+        <v>46287</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11259,13 +11264,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>6.7</v>
+        <v>4.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11308,7 +11308,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 39897-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11322,10 +11322,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45627</v>
+        <v>46289</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11398,7 +11398,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46274</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 7385-2023</t>
+          <t>A 1683-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1534,14 +1534,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44971</v>
+        <v>46034</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,14 +1553,19 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>3.5</v>
+        <v>29.2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1569,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1578,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
         <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1594,486 +1599,481 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Skogsalm
+Talltita</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 17889-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 7385-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44971</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>Bolmört
 Tibast</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 29532-2022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44753</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Backruta
+Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 9956-2022</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>44621</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I14" t="n">
         <v>6.4</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Ögonpyrola
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 29532-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44753</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Backruta
-Hagfingersvamp</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 1683-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46034</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Talltita</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 17889-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15334-2023</t>
+          <t>A 50226-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2083,14 +2083,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45019</v>
+        <v>45943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2104,17 +2104,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>27.3</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2148,42 +2148,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 15334-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45770</v>
+        <v>45019</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,14 +2212,19 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>16.4</v>
+        <v>27.3</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2253,35 +2258,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
     </row>
@@ -2305,7 +2310,7 @@
         <v>45632</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2393,7 +2398,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 3553-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2403,14 +2408,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45943</v>
+        <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2422,23 +2427,18 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2468,42 +2468,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 3553-2026</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46042</v>
+        <v>45770</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,16 +2533,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>16.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 3553-2026 artfynd.xlsx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 3553-2026 karta.png", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 3553-2026 georefererad karta.tif", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 3553-2026 FSC-klagomål.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 3553-2026 FSC-klagomål mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 3553-2026 tillsynsbegäran.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 3553-2026 tillsynsbegäran mail.docx", "A 3553-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 74425-2021</t>
+          <t>A 30868-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3129,14 +3129,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44564</v>
+        <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 29510-2022</t>
+          <t>A 74425-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44753</v>
+        <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3221,13 +3221,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3270,7 +3265,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 29513-2022</t>
+          <t>A 29510-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3287,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,7 +3300,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3348,7 +3343,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30868-2022</t>
+          <t>A 29513-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3358,14 +3353,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44767</v>
+        <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3377,8 +3372,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45236</v>
+        <v>45439</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45769</v>
+        <v>45789</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3971,13 +3971,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>14.6</v>
+        <v>2.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4020,7 +4015,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4030,14 +4025,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45705</v>
+        <v>45635</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4049,13 +4044,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4098,7 +4088,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4112,10 +4102,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45566</v>
+        <v>45247</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4128,7 +4118,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4171,7 +4161,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4185,10 +4175,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45125</v>
+        <v>44919</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4200,13 +4190,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4249,7 +4234,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4263,10 +4248,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45722</v>
+        <v>44858</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4278,13 +4263,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>11.5</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4327,7 +4307,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4341,10 +4321,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44481</v>
+        <v>45548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4357,7 +4337,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4400,7 +4380,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4414,10 +4394,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44858</v>
+        <v>44746</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4429,8 +4409,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4473,7 +4458,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4483,14 +4468,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45737</v>
+        <v>44994</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4504,11 +4489,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4551,7 +4536,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4565,10 +4550,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45635</v>
+        <v>44781</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4580,8 +4565,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>22.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4624,7 +4614,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4638,10 +4628,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44919</v>
+        <v>45566</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4654,7 +4644,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4697,7 +4687,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4707,14 +4697,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45769</v>
+        <v>45995</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4728,11 +4718,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>10.1</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4775,7 +4765,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4789,10 +4779,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45627</v>
+        <v>45442</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4805,7 +4795,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4848,7 +4838,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4858,14 +4848,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45071</v>
+        <v>45925</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4877,13 +4867,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4926,7 +4911,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4940,10 +4925,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45071</v>
+        <v>46077</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4957,11 +4942,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5004,7 +4989,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5018,10 +5003,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45769</v>
+        <v>46077</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5033,8 +5018,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>19.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5077,7 +5067,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5091,10 +5081,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44974</v>
+        <v>46078</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5106,8 +5096,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>8.5</v>
+        <v>18.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5150,7 +5145,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5164,10 +5159,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45442</v>
+        <v>45810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5179,8 +5174,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>22.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5223,7 +5223,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44953</v>
+        <v>46093</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5296,7 +5296,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45771</v>
+        <v>44974</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5325,13 +5325,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>16.8</v>
+        <v>8.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5374,7 +5369,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5384,14 +5379,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45762</v>
+        <v>45071</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5409,7 +5404,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5452,7 +5447,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5466,10 +5461,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45112</v>
+        <v>45071</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5481,8 +5476,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5525,7 +5525,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44998</v>
+        <v>45972</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5554,13 +5554,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5603,7 +5598,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5617,10 +5612,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45632</v>
+        <v>46122</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5632,8 +5627,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5693,7 +5693,7 @@
         <v>44998</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.9</v>
+        <v>3.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5754,7 +5754,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5768,10 +5768,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45160</v>
+        <v>46128</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5783,8 +5783,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5827,7 +5832,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5841,10 +5846,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44764</v>
+        <v>46128</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5856,8 +5861,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>4.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5900,7 +5910,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5910,14 +5920,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45785</v>
+        <v>46128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5935,7 +5945,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.7</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5978,7 +5988,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5992,10 +6002,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45785</v>
+        <v>45503</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6007,13 +6017,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6056,7 +6061,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45627</v>
+        <v>46122</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6085,8 +6090,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2.7</v>
+        <v>6.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6129,7 +6139,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6143,10 +6153,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45222</v>
+        <v>46134</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6158,8 +6168,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>13.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6202,7 +6217,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6216,10 +6231,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45748</v>
+        <v>46134</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6237,7 +6252,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6280,7 +6295,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6290,14 +6305,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45071</v>
+        <v>46135</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6315,7 +6330,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6358,7 +6373,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6372,10 +6387,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45635</v>
+        <v>45722</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6387,8 +6402,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>11.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6431,7 +6451,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6441,14 +6461,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45128</v>
+        <v>46140</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6466,7 +6486,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6509,7 +6529,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6519,14 +6539,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45247</v>
+        <v>45705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6538,8 +6558,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6582,7 +6607,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6592,14 +6617,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45548</v>
+        <v>46010</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6611,8 +6636,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6672,7 +6702,7 @@
         <v>44739</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6728,7 +6758,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6738,14 +6768,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45627</v>
+        <v>45840</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6757,8 +6787,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6801,7 +6836,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6811,14 +6846,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45503</v>
+        <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6830,8 +6865,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6874,7 +6914,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6884,14 +6924,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45810</v>
+        <v>45840</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6905,11 +6945,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>22.6</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6952,7 +6992,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 49311-2022</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6962,14 +7002,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44861</v>
+        <v>45846</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,8 +7021,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7025,7 +7070,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7039,10 +7084,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45439</v>
+        <v>45748</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,8 +7099,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>6.9</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7098,7 +7148,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7112,10 +7162,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45274</v>
+        <v>45819</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7128,7 +7178,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7171,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 49311-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7185,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45193</v>
+        <v>44861</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7201,7 +7251,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>8.4</v>
+        <v>3.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7244,7 +7294,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7254,14 +7304,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45840</v>
+        <v>45821</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7279,7 +7329,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7322,7 +7372,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7332,14 +7382,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45840</v>
+        <v>46094</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7351,13 +7401,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7400,7 +7445,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7410,14 +7455,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45840</v>
+        <v>45071</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7435,7 +7480,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7478,7 +7523,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7488,14 +7533,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45846</v>
+        <v>46150</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7513,7 +7558,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7556,7 +7601,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7570,10 +7615,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45819</v>
+        <v>46150</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7585,8 +7630,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7629,7 +7679,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7643,10 +7693,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45627</v>
+        <v>46150</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7658,8 +7708,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>7.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7702,7 +7757,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7716,10 +7771,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45446</v>
+        <v>46150</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7731,8 +7786,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7775,7 +7835,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7789,10 +7849,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45925</v>
+        <v>46150</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7804,8 +7864,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>11.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7848,7 +7913,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7862,10 +7927,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45972</v>
+        <v>45236</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7878,7 +7943,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7921,7 +7986,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7931,14 +7996,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46010</v>
+        <v>45446</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7950,13 +8015,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7999,7 +8059,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8009,14 +8069,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45789</v>
+        <v>45902</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8028,8 +8088,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8072,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8086,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44994</v>
+        <v>46164</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8101,13 +8166,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8150,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8164,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44781</v>
+        <v>44481</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8179,13 +8239,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>22.9</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8228,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8242,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44746</v>
+        <v>46181</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8259,11 +8314,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8306,7 +8361,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8316,14 +8371,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45995</v>
+        <v>45125</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8337,11 +8392,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8384,7 +8439,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8398,10 +8453,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46077</v>
+        <v>45627</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8413,13 +8468,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>19.5</v>
+        <v>8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8462,7 +8512,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8476,10 +8526,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46078</v>
+        <v>45771</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8493,11 +8543,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>18.6</v>
+        <v>16.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8540,7 +8590,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8554,10 +8604,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46077</v>
+        <v>45160</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8569,13 +8619,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8618,7 +8663,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8632,10 +8677,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46093</v>
+        <v>45635</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8648,7 +8693,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8691,7 +8736,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8705,10 +8750,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46122</v>
+        <v>45769</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8722,11 +8767,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>10.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8769,7 +8814,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8779,14 +8824,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46122</v>
+        <v>45737</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8800,11 +8845,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8847,7 +8892,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8861,10 +8906,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46128</v>
+        <v>45835</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8882,7 +8927,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8925,7 +8970,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8939,10 +8984,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46128</v>
+        <v>45128</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8960,7 +9005,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>8.699999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9003,7 +9048,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9013,14 +9058,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46128</v>
+        <v>45193</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9032,13 +9077,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>2.9</v>
+        <v>8.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9081,7 +9121,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9091,14 +9131,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46134</v>
+        <v>46258</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9116,7 +9156,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>13.2</v>
+        <v>6.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9159,7 +9199,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9169,14 +9209,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46135</v>
+        <v>46213</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9188,13 +9228,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9237,7 +9272,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9251,10 +9286,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46134</v>
+        <v>46223</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9268,7 +9303,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -9315,7 +9350,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9329,10 +9364,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45821</v>
+        <v>46268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9346,11 +9381,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9393,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9403,14 +9438,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46140</v>
+        <v>45627</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9422,13 +9457,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9471,7 +9501,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9485,10 +9515,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46094</v>
+        <v>45274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9501,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9544,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9554,14 +9584,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46150</v>
+        <v>46274</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9579,7 +9609,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>11.8</v>
+        <v>6.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9622,7 +9652,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9632,14 +9662,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46150</v>
+        <v>46274</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9657,7 +9687,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9700,7 +9730,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9710,14 +9740,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46150</v>
+        <v>46274</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9735,7 +9765,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9778,7 +9808,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9788,14 +9818,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46150</v>
+        <v>46274</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9813,7 +9843,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9856,7 +9886,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9870,10 +9900,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46150</v>
+        <v>44953</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9885,13 +9915,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9934,7 +9959,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9944,14 +9969,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45902</v>
+        <v>45112</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9963,13 +9988,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10012,7 +10032,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10026,10 +10046,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46164</v>
+        <v>46239</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10042,7 +10062,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10105,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 38973-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10119,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46181</v>
+        <v>46286</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10114,13 +10134,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10163,7 +10178,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 39234-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10177,10 +10192,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45835</v>
+        <v>46287</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10192,13 +10207,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10241,7 +10251,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 33191-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10255,10 +10265,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46213</v>
+        <v>46246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10270,8 +10280,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10314,7 +10329,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10324,14 +10339,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46258</v>
+        <v>46246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10349,7 +10364,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10392,7 +10407,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10406,10 +10421,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46223</v>
+        <v>46246</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10421,13 +10436,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10470,7 +10480,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 39897-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10484,10 +10494,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46268</v>
+        <v>46289</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10499,13 +10509,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10548,7 +10553,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10558,14 +10563,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46274</v>
+        <v>45627</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10577,13 +10582,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10626,7 +10626,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10636,14 +10636,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46274</v>
+        <v>45222</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10655,13 +10655,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10704,7 +10699,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10714,14 +10709,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46274</v>
+        <v>45762</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10739,7 +10734,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10782,7 +10777,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10792,14 +10787,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46274</v>
+        <v>45769</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10813,11 +10808,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5.9</v>
+        <v>14.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10860,7 +10855,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10874,10 +10869,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46239</v>
+        <v>45769</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10890,7 +10885,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10933,7 +10928,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 38973-2026</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10947,10 +10942,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46286</v>
+        <v>45632</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10963,7 +10958,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11006,7 +11001,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11020,10 +11015,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46246</v>
+        <v>44764</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11036,7 +11031,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11079,7 +11074,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 33191-2026</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11093,10 +11088,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46246</v>
+        <v>44998</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11110,11 +11105,11 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.6</v>
+        <v>6.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11157,7 +11152,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11171,10 +11166,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46246</v>
+        <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11192,7 +11187,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>7.3</v>
+        <v>18</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11235,7 +11230,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 39234-2026</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11249,10 +11244,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46287</v>
+        <v>45785</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11264,8 +11259,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>4.1</v>
+        <v>6.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11308,7 +11308,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 39897-2026</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11322,10 +11322,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46289</v>
+        <v>45627</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11398,7 +11398,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46274</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1683-2026</t>
+          <t>A 9956-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1534,14 +1534,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46034</v>
+        <v>44621</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1559,22 +1559,22 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>29.2</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1599,481 +1599,481 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Ögonpyrola
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 1683-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>Skogsalm
 Talltita</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 17889-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>46122</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="E12" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>2.7</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Tallticka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 29532-2022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44753</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Backruta
+Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 7385-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>44971</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>3.5</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bolmört
 Tibast</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 29532-2022</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44753</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Backruta
-Hagfingersvamp</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 9956-2022</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 15334-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2083,14 +2083,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45943</v>
+        <v>45019</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2104,17 +2104,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.1</v>
+        <v>27.3</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2148,42 +2148,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15334-2023</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45019</v>
+        <v>45770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,19 +2212,14 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>27.3</v>
+        <v>16.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2258,42 +2253,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58307-2024</t>
+          <t>A 50226-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2303,14 +2298,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45632</v>
+        <v>45943</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2322,14 +2317,19 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2363,35 +2363,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
         <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 58307-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45770</v>
+        <v>45632</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>16.4</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 25053-2022</t>
+          <t>A 69104-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44729</v>
+        <v>44530</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3596,8 +3596,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3640,7 +3645,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 25057-2022</t>
+          <t>A 68174-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3654,10 +3659,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44729</v>
+        <v>44526</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3669,8 +3674,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3713,7 +3723,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 69104-2021</t>
+          <t>A 25053-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3723,14 +3733,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44530</v>
+        <v>44729</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3742,13 +3752,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3791,7 +3796,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 68174-2021</t>
+          <t>A 25057-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3805,10 +3810,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44526</v>
+        <v>44729</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3820,13 +3825,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3869,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45439</v>
+        <v>45236</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45789</v>
+        <v>44858</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45635</v>
+        <v>45071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,8 +4044,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4088,7 +4093,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4102,10 +4107,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45247</v>
+        <v>45071</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4117,8 +4122,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4161,7 +4171,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4175,10 +4185,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44919</v>
+        <v>45771</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4190,8 +4200,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>16.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4234,7 +4249,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4248,10 +4263,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44858</v>
+        <v>45627</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4264,7 +4279,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4307,7 +4322,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4321,10 +4336,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45548</v>
+        <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4336,8 +4351,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4380,7 +4400,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4390,14 +4410,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44746</v>
+        <v>46010</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4411,11 +4431,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4458,7 +4478,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4472,10 +4492,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44994</v>
+        <v>45635</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4487,13 +4507,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4536,7 +4551,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4550,10 +4565,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44781</v>
+        <v>45789</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4565,13 +4580,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>22.9</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4614,7 +4624,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4628,10 +4638,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45566</v>
+        <v>44739</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4644,7 +4654,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4687,7 +4697,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 49311-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4697,14 +4707,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45995</v>
+        <v>44861</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4716,13 +4726,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4765,7 +4770,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4779,10 +4784,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45442</v>
+        <v>45548</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4795,7 +4800,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4855,7 +4860,7 @@
         <v>45925</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4911,7 +4916,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4925,10 +4930,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46077</v>
+        <v>44994</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4942,11 +4947,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4989,7 +4994,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5003,10 +5008,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46077</v>
+        <v>44781</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5020,11 +5025,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>19.5</v>
+        <v>22.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5067,7 +5072,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5081,10 +5086,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46078</v>
+        <v>44746</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5098,11 +5103,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>18.6</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5162,7 +5167,7 @@
         <v>45810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5223,7 +5228,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5233,14 +5238,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46093</v>
+        <v>45995</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5252,8 +5257,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5296,7 +5306,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5310,10 +5320,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44974</v>
+        <v>46077</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5325,8 +5335,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>8.5</v>
+        <v>19.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5369,7 +5384,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5379,14 +5394,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45071</v>
+        <v>46078</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5400,11 +5415,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>18.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5447,7 +5462,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5461,10 +5476,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45071</v>
+        <v>46077</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5478,11 +5493,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5525,7 +5540,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5539,10 +5554,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45972</v>
+        <v>45446</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5555,7 +5570,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5598,7 +5613,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5612,10 +5627,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46122</v>
+        <v>45566</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5627,13 +5642,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5676,7 +5686,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5690,10 +5700,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44998</v>
+        <v>46093</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5705,13 +5715,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5754,7 +5759,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5768,10 +5773,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46128</v>
+        <v>45635</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5783,13 +5788,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5832,7 +5832,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46128</v>
+        <v>45972</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5861,13 +5861,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>8.699999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5910,7 +5905,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5920,14 +5915,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46128</v>
+        <v>44919</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5939,13 +5934,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5988,7 +5978,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6002,10 +5992,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45503</v>
+        <v>46122</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6017,8 +6007,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6078,7 +6073,7 @@
         <v>46122</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6139,7 +6134,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6153,10 +6148,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46134</v>
+        <v>46128</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6174,7 +6169,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>13.2</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6217,7 +6212,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6231,10 +6226,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46134</v>
+        <v>46128</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6252,7 +6247,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6295,7 +6290,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6309,10 +6304,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46135</v>
+        <v>46128</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6330,7 +6325,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6373,7 +6368,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6387,10 +6382,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45722</v>
+        <v>46134</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6408,7 +6403,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>11.5</v>
+        <v>13.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6451,7 +6446,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20583-2026</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6461,14 +6456,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46140</v>
+        <v>46135</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6486,7 +6481,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6529,7 +6524,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6539,14 +6534,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45705</v>
+        <v>46134</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6560,11 +6555,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6607,7 +6602,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6617,14 +6612,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46010</v>
+        <v>45112</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6636,13 +6631,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6685,7 +6675,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6695,14 +6685,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44739</v>
+        <v>45840</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6714,8 +6704,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6758,7 +6753,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6775,7 +6770,7 @@
         <v>45840</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6793,7 +6788,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6836,7 +6831,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6853,7 +6848,7 @@
         <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6871,7 +6866,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6914,7 +6909,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6928,10 +6923,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45840</v>
+        <v>45846</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6949,7 +6944,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6992,7 +6987,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7002,14 +6997,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45846</v>
+        <v>45819</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7021,13 +7016,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7070,7 +7060,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7084,10 +7074,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45748</v>
+        <v>45222</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7099,13 +7089,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7148,7 +7133,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7162,10 +7147,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45819</v>
+        <v>45821</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7177,8 +7162,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7221,7 +7211,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 49311-2022</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7225,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44861</v>
+        <v>45247</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7251,7 +7241,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7294,7 +7284,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 20583-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7304,14 +7294,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45821</v>
+        <v>46140</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7329,7 +7319,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7389,7 +7379,7 @@
         <v>46094</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7445,7 +7435,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7459,10 +7449,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45071</v>
+        <v>46150</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7480,7 +7470,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>11.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7540,7 +7530,7 @@
         <v>46150</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7618,7 +7608,7 @@
         <v>46150</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7696,7 +7686,7 @@
         <v>46150</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7774,7 +7764,7 @@
         <v>46150</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7835,7 +7825,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7849,10 +7839,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46150</v>
+        <v>45274</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7864,13 +7854,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>11.8</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7913,7 +7898,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7923,14 +7908,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45236</v>
+        <v>45902</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7942,8 +7927,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7986,7 +7976,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8000,10 +7990,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45446</v>
+        <v>46164</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8016,7 +8006,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8059,7 +8049,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8069,14 +8059,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45902</v>
+        <v>45627</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8088,13 +8078,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8122,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8136,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46164</v>
+        <v>46181</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8166,8 +8151,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8200,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8220,14 +8210,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44481</v>
+        <v>45705</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8239,8 +8229,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>0.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8278,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8292,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46181</v>
+        <v>45722</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8318,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8361,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8375,10 +8370,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45125</v>
+        <v>44481</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8390,13 +8385,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8439,7 +8429,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8449,14 +8439,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45627</v>
+        <v>45737</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8468,8 +8458,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8512,7 +8507,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8526,10 +8521,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45771</v>
+        <v>45835</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8547,7 +8542,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>16.8</v>
+        <v>5.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8590,7 +8585,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8604,10 +8599,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45160</v>
+        <v>45769</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8619,8 +8614,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>10.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8677,10 +8677,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45635</v>
+        <v>45769</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8736,7 +8736,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45769</v>
+        <v>45442</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8765,13 +8765,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>10.1</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8814,7 +8809,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8824,14 +8819,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45737</v>
+        <v>46213</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8843,13 +8838,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8892,7 +8882,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8902,14 +8892,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45835</v>
+        <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8927,7 +8917,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8970,7 +8960,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8984,10 +8974,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45128</v>
+        <v>44953</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8999,13 +8989,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9048,7 +9033,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9062,10 +9047,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45193</v>
+        <v>45762</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9077,8 +9062,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>8.4</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9121,7 +9111,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9131,14 +9121,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46258</v>
+        <v>44998</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9152,11 +9142,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9199,7 +9189,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9213,10 +9203,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46213</v>
+        <v>46223</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9228,8 +9218,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9272,7 +9267,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9286,10 +9281,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46223</v>
+        <v>46268</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9303,11 +9298,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9350,7 +9345,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9364,10 +9359,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46268</v>
+        <v>45160</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9379,13 +9374,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9428,7 +9418,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9438,14 +9428,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45627</v>
+        <v>46274</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9457,8 +9447,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9501,7 +9496,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9511,14 +9506,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45274</v>
+        <v>46274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9530,8 +9525,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>46274</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9669,7 +9669,7 @@
         <v>46274</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9730,7 +9730,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9740,14 +9740,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46274</v>
+        <v>45748</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9808,7 +9808,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9818,14 +9818,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46274</v>
+        <v>45071</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9886,7 +9886,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9900,10 +9900,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44953</v>
+        <v>46239</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 38973-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9973,10 +9973,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45112</v>
+        <v>46286</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10032,7 +10032,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10046,10 +10046,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46239</v>
+        <v>45627</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10105,7 +10105,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 38973-2026</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10119,10 +10119,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46286</v>
+        <v>45503</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10178,7 +10178,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 39234-2026</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10192,10 +10192,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46287</v>
+        <v>46246</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10268,7 +10268,7 @@
         <v>46246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 39234-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46246</v>
+        <v>46287</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10358,13 +10358,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>7.3</v>
+        <v>4.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10407,7 +10402,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10421,10 +10416,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46246</v>
+        <v>45439</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10437,7 +10432,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10497,7 +10492,7 @@
         <v>46289</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10553,7 +10548,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10567,10 +10562,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45627</v>
+        <v>45193</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10583,7 +10578,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10626,7 +10621,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10640,10 +10635,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45222</v>
+        <v>46246</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10655,8 +10650,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>7.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10699,7 +10699,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45762</v>
+        <v>45769</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10730,11 +10730,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>14.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10777,7 +10777,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10791,10 +10791,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45769</v>
+        <v>45125</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10808,11 +10808,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>14.6</v>
+        <v>3.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10855,7 +10855,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10869,10 +10869,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45769</v>
+        <v>44974</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10945,7 +10945,7 @@
         <v>45632</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11015,10 +11015,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44764</v>
+        <v>44998</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11030,8 +11030,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>4.5</v>
+        <v>6.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11074,7 +11079,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11088,10 +11093,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44998</v>
+        <v>44764</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11103,13 +11108,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>6.9</v>
+        <v>4.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11152,7 +11152,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11169,7 +11169,7 @@
         <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>18</v>
+        <v>6.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11230,7 +11230,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11247,7 +11247,7 @@
         <v>45785</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>6.7</v>
+        <v>18</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11325,7 +11325,7 @@
         <v>45627</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46274</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>44621</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>46034</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>46122</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>44753</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45019</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>45943</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45632</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44530</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>44526</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>44729</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>44729</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45236</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44858</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45071</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45771</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>45627</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>46010</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>45635</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>45789</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44739</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>44861</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>45548</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45925</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44994</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>44781</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44746</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>45810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>45995</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>46077</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>46078</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>46077</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>45446</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>45566</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>46093</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>45635</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>45972</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44919</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>46122</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>46122</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>46128</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>46128</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46128</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>46134</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>46135</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>46134</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45112</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>45840</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>45840</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45846</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45819</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45222</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45821</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>45247</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>46140</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>46094</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>46150</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>46150</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>46150</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>46150</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>46150</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45274</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>45902</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>46164</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45627</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>46181</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>45705</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>45722</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>44481</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>45737</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>45835</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45769</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45769</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45442</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>46213</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44953</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45762</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44998</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>46223</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>46268</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45160</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>46274</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>46274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>46274</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>46274</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45748</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>45071</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>46239</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>46286</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>45627</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>45503</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>46246</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>46246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>46287</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45439</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>46289</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>45193</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>46246</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>45769</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>45125</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>44974</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45632</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>44998</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>44764</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>45785</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45627</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46274</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>44621</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>46034</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>46122</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>44753</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45019</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>45943</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45632</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44530</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>44526</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>44729</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>44729</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45236</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44858</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45071</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45771</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>45627</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>46010</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>45635</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>45789</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44739</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>44861</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>45548</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45925</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44994</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>44781</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44746</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>45810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>45995</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>46077</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>46078</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>46077</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>45446</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>45566</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>46093</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>45635</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>45972</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44919</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>46122</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>46122</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>46128</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>46128</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46128</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>46134</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>46135</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>46134</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45112</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>45840</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>45840</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45846</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45819</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45222</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45821</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>45247</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>46140</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>46094</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>46150</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>46150</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>46150</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>46150</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>46150</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45274</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>45902</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>46164</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45627</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>46181</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>45705</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>45722</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>44481</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>45737</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>45835</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45769</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45769</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45442</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>46213</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44953</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45762</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44998</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>46223</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>46268</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45160</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>46274</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>46274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>46274</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>46274</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45748</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>45071</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>46239</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>46286</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>45627</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>45503</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>46246</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>46246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>46287</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45439</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>46289</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>45193</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>46246</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>45769</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>45125</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>44974</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45632</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>44998</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>44764</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>45785</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45627</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46274</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 9956-2022</t>
+          <t>A 29532-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44621</v>
+        <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,22 +1553,17 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1583,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1599,481 +1594,486 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Backruta
+Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 1683-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Talltita</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 7385-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44971</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Bolmört
+Tibast</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17889-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9956-2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Ögonpyrola
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 1683-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46034</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Talltita</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 17889-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 29532-2022</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44753</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Backruta
-Hagfingersvamp</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 7385-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44971</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Tibast</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15334-2023</t>
+          <t>A 50226-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2083,14 +2083,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45019</v>
+        <v>45943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2104,17 +2104,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>27.3</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2148,42 +2148,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 19550-2025</t>
+          <t>A 15334-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45770</v>
+        <v>45019</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,14 +2212,19 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>16.4</v>
+        <v>27.3</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2253,42 +2258,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 15334-2023 artfynd.xlsx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 15334-2023 karta.png", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 15334-2023 georefererad karta.tif", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 15334-2023 FSC-klagomål.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 15334-2023 FSC-klagomål mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 15334-2023 tillsynsbegäran.docx", "A 15334-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 15334-2023 tillsynsbegäran mail.docx", "A 15334-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 58307-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2298,14 +2303,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45943</v>
+        <v>45632</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2317,19 +2322,14 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2363,35 +2363,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 50226-2025 artfynd.xlsx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 50226-2025 karta.png", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 50226-2025 georefererad karta.tif", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 50226-2025 FSC-klagomål.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 50226-2025 FSC-klagomål mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 50226-2025 tillsynsbegäran.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 50226-2025 tillsynsbegäran mail.docx", "A 50226-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
         <v/>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
         <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58307-2024</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45632</v>
+        <v>45770</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="I19" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2573,35 +2573,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 58307-2024 artfynd.xlsx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 19550-2025 artfynd.xlsx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 58307-2024 karta.png", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 19550-2025 karta.png", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 58307-2024 georefererad karta.tif", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 19550-2025 georefererad karta.tif", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 58307-2024 FSC-klagomål.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 19550-2025 FSC-klagomål.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 58307-2024 FSC-klagomål mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 19550-2025 FSC-klagomål mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 58307-2024 tillsynsbegäran.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 19550-2025 tillsynsbegäran.docx", "A 19550-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 58307-2024 tillsynsbegäran mail.docx", "A 58307-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 19550-2025 tillsynsbegäran mail.docx", "A 19550-2025")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>44533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44586</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>44559</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44776</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44767</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44753</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44872</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 69104-2021</t>
+          <t>A 25053-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44530</v>
+        <v>44729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3596,13 +3596,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3645,7 +3640,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 68174-2021</t>
+          <t>A 25057-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3659,10 +3654,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44526</v>
+        <v>44729</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3674,13 +3669,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3723,7 +3713,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25053-2022</t>
+          <t>A 69104-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3733,14 +3723,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44729</v>
+        <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3752,8 +3742,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3796,7 +3791,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25057-2022</t>
+          <t>A 68174-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3810,10 +3805,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44729</v>
+        <v>44526</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3825,8 +3820,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3869,7 +3869,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54804-2023</t>
+          <t>A 20909-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45236</v>
+        <v>45439</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48261-2022</t>
+          <t>A 57855-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44858</v>
+        <v>45247</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22482-2023</t>
+          <t>A 48261-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45071</v>
+        <v>44858</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,13 +4044,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4093,7 +4088,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22485-2023</t>
+          <t>A 62095-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4107,10 +4102,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45071</v>
+        <v>44919</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4122,13 +4117,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4171,7 +4161,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19888-2025</t>
+          <t>A 42844-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4185,10 +4175,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45771</v>
+        <v>45566</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4200,13 +4190,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>16.8</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4249,7 +4234,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56694-2024</t>
+          <t>A 26652-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4263,10 +4248,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45627</v>
+        <v>45810</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4278,8 +4263,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>8</v>
+        <v>22.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4322,7 +4312,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33357-2023</t>
+          <t>A 21679-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4336,10 +4326,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45128</v>
+        <v>45442</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4351,13 +4341,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4400,7 +4385,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 63305-2025</t>
+          <t>A 33238-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4414,10 +4399,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46010</v>
+        <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4435,7 +4420,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4478,7 +4463,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 58594-2024</t>
+          <t>A 33232-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4488,14 +4473,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45635</v>
+        <v>45840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4507,8 +4492,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4551,7 +4541,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22590-2025</t>
+          <t>A 33236-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4561,14 +4551,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45789</v>
+        <v>45840</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4580,8 +4570,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4624,7 +4619,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26509-2022</t>
+          <t>A 8264-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44739</v>
+        <v>44974</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4654,7 +4649,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4697,7 +4692,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 49311-2022</t>
+          <t>A 34374-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4707,14 +4702,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44861</v>
+        <v>45846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4726,8 +4721,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 39157-2024</t>
+          <t>A 28425-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45548</v>
+        <v>45819</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4843,7 +4843,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46359-2025</t>
+          <t>A 22482-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45925</v>
+        <v>45071</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4872,8 +4872,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4916,7 +4921,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11660-2023</t>
+          <t>A 22485-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4930,10 +4935,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44994</v>
+        <v>45071</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4947,11 +4952,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4994,7 +4999,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32249-2022</t>
+          <t>A 46359-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5008,10 +5013,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44781</v>
+        <v>45925</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5023,13 +5028,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>22.9</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28249-2022</t>
+          <t>A 12125-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44746</v>
+        <v>44998</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5103,11 +5103,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5150,7 +5150,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26652-2025</t>
+          <t>A 28249-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45810</v>
+        <v>44746</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5181,11 +5181,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>22.6</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60374-2025</t>
+          <t>A 11660-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5238,14 +5238,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45995</v>
+        <v>44994</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10520-2026</t>
+          <t>A 32249-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5320,10 +5320,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46077</v>
+        <v>44781</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5337,11 +5337,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>19.5</v>
+        <v>22.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5384,7 +5384,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10686-2026</t>
+          <t>A 31231-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46078</v>
+        <v>45503</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5413,13 +5413,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>18.6</v>
+        <v>6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5462,7 +5457,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10526-2026</t>
+          <t>A 60374-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5472,14 +5467,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46077</v>
+        <v>45995</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5493,11 +5488,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5540,7 +5535,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22323-2024</t>
+          <t>A 10526-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5554,10 +5549,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45446</v>
+        <v>46077</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5569,8 +5564,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>6.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 42844-2024</t>
+          <t>A 10520-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45566</v>
+        <v>46077</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5642,8 +5642,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>19.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5686,7 +5691,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13079-2026</t>
+          <t>A 10686-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5700,10 +5705,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46093</v>
+        <v>46078</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5715,8 +5720,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>18.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5759,7 +5769,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58464-2024</t>
+          <t>A 13079-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5773,10 +5783,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45635</v>
+        <v>46093</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5789,7 +5799,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5832,7 +5842,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 55794-2025</t>
+          <t>A 10820-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5846,10 +5856,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45972</v>
+        <v>45722</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5861,8 +5871,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5905,7 +5920,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62095-2022</t>
+          <t>A 7380-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5915,14 +5930,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44919</v>
+        <v>45705</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5934,8 +5949,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5978,7 +5998,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17886-2026</t>
+          <t>A 55794-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5992,10 +6012,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46122</v>
+        <v>45972</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6007,13 +6027,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6056,7 +6071,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17893-2026</t>
+          <t>A 26509-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6070,10 +6085,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46122</v>
+        <v>44739</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6085,13 +6100,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6134,7 +6144,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18782-2026</t>
+          <t>A 15812-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6148,10 +6158,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46128</v>
+        <v>45748</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6169,7 +6179,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6212,7 +6222,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18781-2026</t>
+          <t>A 49311-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6226,10 +6236,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46128</v>
+        <v>44861</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6241,13 +6251,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>8.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6290,7 +6295,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18783-2026</t>
+          <t>A 17886-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6300,14 +6305,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46128</v>
+        <v>46122</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6325,7 +6330,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6368,7 +6373,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19707-2026</t>
+          <t>A 18782-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6382,10 +6387,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46134</v>
+        <v>46128</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6403,7 +6408,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>13.2</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6446,7 +6451,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19825-2026</t>
+          <t>A 18781-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6456,14 +6461,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46135</v>
+        <v>46128</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6481,7 +6486,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6524,7 +6529,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 19708-2026</t>
+          <t>A 18783-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6534,14 +6539,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46134</v>
+        <v>46128</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6559,7 +6564,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6602,7 +6607,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30630-2023</t>
+          <t>A 17893-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6616,10 +6621,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45112</v>
+        <v>46122</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6631,8 +6636,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6675,7 +6685,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33236-2025</t>
+          <t>A 19707-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6685,14 +6695,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45840</v>
+        <v>46134</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6710,7 +6720,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.9</v>
+        <v>13.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6753,7 +6763,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33232-2025</t>
+          <t>A 22484-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6763,14 +6773,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45840</v>
+        <v>45071</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6788,7 +6798,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6831,7 +6841,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33238-2025</t>
+          <t>A 19708-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6841,14 +6851,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45840</v>
+        <v>46134</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6866,7 +6876,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6909,7 +6919,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34374-2025</t>
+          <t>A 19825-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6923,10 +6933,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45846</v>
+        <v>46135</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6944,7 +6954,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6987,7 +6997,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28425-2025</t>
+          <t>A 63305-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6997,14 +7007,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45819</v>
+        <v>46010</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7016,8 +7026,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7060,7 +7075,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 51586-2023</t>
+          <t>A 54804-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7074,10 +7089,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45222</v>
+        <v>45236</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7090,7 +7105,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7133,7 +7148,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29073-2025</t>
+          <t>A 22590-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7147,10 +7162,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45821</v>
+        <v>45789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7162,13 +7177,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7211,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 57855-2023</t>
+          <t>A 22323-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7225,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45247</v>
+        <v>45446</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7241,7 +7251,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7301,7 +7311,7 @@
         <v>46140</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7362,7 +7372,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13391-2026</t>
+          <t>A 56739-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7376,10 +7386,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46094</v>
+        <v>44481</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7392,7 +7402,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7435,7 +7445,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21891-2026</t>
+          <t>A 29073-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7449,10 +7459,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46150</v>
+        <v>45821</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7470,7 +7480,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>11.8</v>
+        <v>6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7523,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21890-2026</t>
+          <t>A 13391-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7527,10 +7537,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46150</v>
+        <v>46094</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7542,13 +7552,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7591,7 +7596,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21888-2026</t>
+          <t>A 33007-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7605,10 +7610,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46150</v>
+        <v>45125</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7626,7 +7631,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7669,7 +7674,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21889-2026</t>
+          <t>A 21890-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7686,7 +7691,7 @@
         <v>46150</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7704,7 +7709,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.1</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7747,7 +7752,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21892-2026</t>
+          <t>A 21888-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7764,7 +7769,7 @@
         <v>46150</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7782,7 +7787,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7825,7 +7830,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 63480-2023</t>
+          <t>A 21889-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7839,10 +7844,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45274</v>
+        <v>46150</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7854,8 +7859,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>7.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7898,7 +7908,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41644-2025</t>
+          <t>A 21892-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7908,14 +7918,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45902</v>
+        <v>46150</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7929,11 +7939,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7976,7 +7986,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23646-2026</t>
+          <t>A 21891-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7990,10 +8000,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46164</v>
+        <v>46150</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8005,8 +8015,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>6.8</v>
+        <v>11.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8049,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 56698-2024</t>
+          <t>A 56694-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8066,7 +8081,7 @@
         <v>45627</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8079,7 +8094,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8122,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26057-2026</t>
+          <t>A 41644-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8132,14 +8147,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46181</v>
+        <v>45902</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8153,11 +8168,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8200,7 +8215,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 7380-2025</t>
+          <t>A 19888-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8210,14 +8225,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45705</v>
+        <v>45771</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8231,11 +8246,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.2</v>
+        <v>16.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8278,7 +8293,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 10820-2025</t>
+          <t>A 37955-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8292,10 +8307,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45722</v>
+        <v>45160</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8307,13 +8322,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>11.5</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8366,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56739-2021</t>
+          <t>A 58464-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8370,10 +8380,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44481</v>
+        <v>45635</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8386,7 +8396,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8439,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13697-2025</t>
+          <t>A 19156-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8439,14 +8449,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45737</v>
+        <v>45769</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8464,7 +8474,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>10.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8507,7 +8517,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32004-2025</t>
+          <t>A 23646-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8521,10 +8531,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45835</v>
+        <v>46164</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8536,13 +8546,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8585,7 +8590,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19156-2025</t>
+          <t>A 13697-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8595,14 +8600,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45769</v>
+        <v>45737</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8620,7 +8625,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>10.1</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8663,7 +8668,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19153-2025</t>
+          <t>A 26057-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8677,10 +8682,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45769</v>
+        <v>46181</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8692,8 +8697,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8736,7 +8746,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 21679-2024</t>
+          <t>A 33357-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8750,10 +8760,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45442</v>
+        <v>45128</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8765,8 +8775,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8809,7 +8824,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31014-2026</t>
+          <t>A 45390-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8823,10 +8838,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46213</v>
+        <v>45193</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8839,7 +8854,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>8.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8882,7 +8897,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34766-2026</t>
+          <t>A 32004-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8892,14 +8907,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46258</v>
+        <v>45835</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8917,7 +8932,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8960,7 +8975,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4264-2023</t>
+          <t>A 56698-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8974,10 +8989,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44953</v>
+        <v>45627</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8990,7 +9005,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9033,7 +9048,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 18463-2025</t>
+          <t>A 63480-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9047,10 +9062,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45762</v>
+        <v>45274</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9062,13 +9077,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9111,7 +9121,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 12125-2023</t>
+          <t>A 31014-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9125,10 +9135,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44998</v>
+        <v>46213</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9140,13 +9150,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9189,7 +9194,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31482-2026</t>
+          <t>A 4264-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9203,10 +9208,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46223</v>
+        <v>44953</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9218,13 +9223,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9267,7 +9267,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 36365-2026</t>
+          <t>A 31482-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46268</v>
+        <v>46223</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9298,11 +9298,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9345,7 +9345,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 37955-2023</t>
+          <t>A 30630-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9359,10 +9359,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45160</v>
+        <v>45112</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 37231-2026</t>
+          <t>A 36365-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9428,14 +9428,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46274</v>
+        <v>46268</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9449,11 +9449,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9496,7 +9496,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 37234-2026</t>
+          <t>A 37235-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9513,7 +9513,7 @@
         <v>46274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37235-2026</t>
+          <t>A 37231-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9591,7 +9591,7 @@
         <v>46274</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9652,7 +9652,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 37228-2026</t>
+          <t>A 37234-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9669,7 +9669,7 @@
         <v>46274</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9730,7 +9730,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 15812-2025</t>
+          <t>A 37228-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9740,14 +9740,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45748</v>
+        <v>46274</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9808,7 +9808,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22484-2023</t>
+          <t>A 32433-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9822,10 +9822,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45071</v>
+        <v>46239</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9837,13 +9837,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9886,7 +9881,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 32433-2026</t>
+          <t>A 38973-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9900,10 +9895,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46239</v>
+        <v>46286</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9916,7 +9911,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9959,7 +9954,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 38973-2026</t>
+          <t>A 56699-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9973,10 +9968,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46286</v>
+        <v>45627</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9989,7 +9984,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10032,7 +10027,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56699-2024</t>
+          <t>A 51586-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10046,10 +10041,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45627</v>
+        <v>45222</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10062,7 +10057,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10105,7 +10100,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 31231-2024</t>
+          <t>A 39234-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10119,10 +10114,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45503</v>
+        <v>46287</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10135,7 +10130,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10178,7 +10173,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 33322-2026</t>
+          <t>A 18463-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10192,10 +10187,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46246</v>
+        <v>45762</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10207,8 +10202,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10268,7 +10268,7 @@
         <v>46246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 39234-2026</t>
+          <t>A 33322-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46287</v>
+        <v>46246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10402,7 +10402,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 20909-2024</t>
+          <t>A 39897-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45439</v>
+        <v>46289</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.9</v>
+        <v>4.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10475,7 +10475,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 39897-2026</t>
+          <t>A 19213-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10489,10 +10489,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46289</v>
+        <v>45769</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10504,8 +10504,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>4.2</v>
+        <v>14.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10548,7 +10553,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 45390-2023</t>
+          <t>A 19153-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10562,10 +10567,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45193</v>
+        <v>45769</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10578,7 +10583,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10621,7 +10626,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 33193-2026</t>
+          <t>A 58310-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10635,10 +10640,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46246</v>
+        <v>45632</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10650,13 +10655,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>7.3</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10699,7 +10699,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 19213-2025</t>
+          <t>A 30813-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45769</v>
+        <v>44764</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10728,13 +10728,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>14.6</v>
+        <v>4.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10777,7 +10772,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 33007-2023</t>
+          <t>A 12121-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10791,10 +10786,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45125</v>
+        <v>44998</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10808,11 +10803,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.7</v>
+        <v>6.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10855,7 +10850,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 8264-2023</t>
+          <t>A 22118-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10869,10 +10864,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44974</v>
+        <v>45785</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10884,8 +10879,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>8.5</v>
+        <v>18</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10928,7 +10928,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 58310-2024</t>
+          <t>A 22117-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10942,10 +10942,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45632</v>
+        <v>45785</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10957,8 +10957,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11001,7 +11006,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 12121-2023</t>
+          <t>A 56704-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11015,10 +11020,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44998</v>
+        <v>45627</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11030,13 +11035,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>6.9</v>
+        <v>2.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11079,7 +11079,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 30813-2022</t>
+          <t>A 58594-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11093,10 +11093,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44764</v>
+        <v>45635</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11152,7 +11152,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 22117-2025</t>
+          <t>A 33193-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11166,10 +11166,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45785</v>
+        <v>46246</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11230,7 +11230,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 22118-2025</t>
+          <t>A 39157-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11244,10 +11244,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45785</v>
+        <v>45548</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11259,13 +11259,8 @@
           <t>FAGERSTA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>18</v>
+        <v>1.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11308,7 +11303,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 56704-2024</t>
+          <t>A 34766-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11318,14 +11313,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45627</v>
+        <v>46258</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11337,8 +11332,13 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11398,7 +11398,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45840</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S 2213-2026</t>
+          <t>S 2358-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11941,10 +11941,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46258</v>
+        <v>46274</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12005,7 +12005,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S 2358-2026</t>
+          <t>S 2213-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12019,10 +12019,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46274</v>
+        <v>46258</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.9</v>
+        <v>6.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>

--- a/Översikt FAGERSTA.xlsx
+++ b/Översikt FAGERSTA.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44747</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45733</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45758</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44747</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45947</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 29532-2022</t>
+          <t>A 9956-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44753</v>
+        <v>44621</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,17 +1553,22 @@
           <t>FAGERSTA</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1578,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1594,486 +1599,481 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Ögonpyrola
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 1683-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Talltita</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 17889-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 29532-2022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44753</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Backruta
 Hagfingersvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 29532-2022 artfynd.xlsx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 29532-2022 karta.png", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 29532-2022 georefererad karta.tif", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 29532-2022 FSC-klagomål.docx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 29532-2022 FSC-klagomål mail.docx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 29532-2022 tillsynsbegäran.docx", "A 29532-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 29532-2022 tillsynsbegäran mail.docx", "A 29532-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 1683-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46034</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="J11" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 7385-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44971</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FAGERSTA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Talltita</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 1683-2026 artfynd.xlsx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 1683-2026 karta.png", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 1683-2026 georefererad karta.tif", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 1683-2026 FSC-klagomål.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 1683-2026 FSC-klagomål mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 1683-2026 tillsynsbegäran.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 1683-2026 tillsynsbegäran mail.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/fåglar/A 1683-2026 prioriterade fågelarter.docx", "A 1683-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 7385-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44971</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bolmört
 Tibast</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 7385-2023 artfynd.xlsx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 7385-2023 karta.png", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 7385-2023 georefererad karta.tif", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 7385-2023 FSC-klagomål.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 7385-2023 FSC-klagomål mail.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 7385-2023 tillsynsbegäran.docx", "A 7385-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 7385-2023 tillsynsbegäran mail.docx", "A 7385-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17889-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 17889-2026 artfynd.xlsx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 17889-2026 karta.png", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 17889-2026 georefererad karta.tif", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 17889-2026 FSC-klagomål.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 17889-2026 FSC-klagomål mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 17889-2026 tillsynsbegäran.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 17889-2026 tillsynsbegäran mail.docx", "A 17889-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 9956-2022</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FAGERSTA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/artfynd/A 9956-2022 artfynd.xlsx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor/A 9956-2022 karta.png", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/kartor_geotiff/A 9956-2022 georefererad karta.tif", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomål/A 9956-2022 FSC-klagomål.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/klagomålsmail/A 9956-2022 FSC-klagomål mail.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsyn/A 9956-2022 tillsynsbegäran.docx", "A 9956-2022")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1982/tillsynsmail/A 9956-2022 tillsynsbegäran mail.docx", "A 9956-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 50226-2025</t>
+          <t>A 19550-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2083,14 +2083,14 @@
   